--- a/Mappage.xlsx
+++ b/Mappage.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="867" uniqueCount="306">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1082" uniqueCount="385">
   <si>
     <t>Composant</t>
   </si>
@@ -38,78 +38,156 @@
     <t>Appareil Déplacement de Flux</t>
   </si>
   <si>
-    <t>CVC_EQG_CTA_Systemair Geniox Go 12:Servitude gauche</t>
+    <t>CVC_EQH_Circulateur double_Grundfos MAGNA3:MAGNA3 D 32-40 - 97924449</t>
+  </si>
+  <si>
+    <t>MAGNA3 D 32-40 - 97924449</t>
   </si>
   <si>
     <t>IfcFlowMovingDevice</t>
   </si>
   <si>
-    <t>09_CTA</t>
-  </si>
-  <si>
-    <t>CVC_EQH_Circulateur double_Grundfos MAGNA3D:MAGNA3 D 32-40</t>
-  </si>
-  <si>
-    <t>20_Pompe</t>
-  </si>
-  <si>
-    <t>CVC_EQH_Circulateur simple_Grundfos MAGNA3:MAGNA3 25-40 N</t>
-  </si>
-  <si>
-    <t>CVC_EQH_Extracteur_France Air Canal Fast ECM:Extracteur VMC</t>
-  </si>
-  <si>
-    <t>10_Extracteur désenfumage</t>
-  </si>
-  <si>
-    <t>CVC_EQH_Préparateur ECS_Atlantic Rubis Evo:SI 206 DD</t>
-  </si>
-  <si>
-    <t>24_Ballon ECS</t>
+    <t>Pompe</t>
+  </si>
+  <si>
+    <t>CVC_EQV_CTA double flux_Systemair Geniox Go 12:Unité intérieure - servitude gauche</t>
+  </si>
+  <si>
+    <t>Unité intérieure - servitude gauche</t>
+  </si>
+  <si>
+    <t>CTA</t>
+  </si>
+  <si>
+    <t>CVC_EQV_Extracteur_Atlantic Copernic H:Caisson extraction simple flux C4</t>
+  </si>
+  <si>
+    <t>Caisson extraction simple flux C4</t>
+  </si>
+  <si>
+    <t>Extracteur désenfumage</t>
   </si>
   <si>
     <t>Appareil de Stockage de Flux</t>
   </si>
   <si>
-    <t>CVC_EQH_Ballon de stockage ECS_Atlantic Corhydro:900 L</t>
-  </si>
-  <si>
-    <t>900 L</t>
+    <t>CVC_ACA_Vase d'expansion_Reflex N:N 80</t>
+  </si>
+  <si>
+    <t>N 80</t>
   </si>
   <si>
     <t>IfcFlowStorageDevice</t>
   </si>
   <si>
+    <t>Vase à expansion</t>
+  </si>
+  <si>
+    <t>CVC_EQH_Pot d'injection acier:11 L - 17703</t>
+  </si>
+  <si>
+    <t>11 L - 17703</t>
+  </si>
+  <si>
+    <t>Accessoires de Canalisations</t>
+  </si>
+  <si>
+    <t>Appareil de Traitement de Flux</t>
+  </si>
+  <si>
+    <t>CVC_ACA_Séparateur de boues magnétique_Flamco Clean Smart:Clean Smart 65 F - DN65</t>
+  </si>
+  <si>
+    <t>IfcFlowTreatmentDevice</t>
+  </si>
+  <si>
+    <t>Hors TND</t>
+  </si>
+  <si>
+    <t>CVC_EQH_Séparateur d'air et de boues_Flamco Clean Smart:Clean Smart 65 F - DN65</t>
+  </si>
+  <si>
+    <t>CVS_Filtre à tamis:DN selon instance</t>
+  </si>
+  <si>
+    <t>Accessoires de gaines</t>
+  </si>
+  <si>
+    <t>PLB_EQH_Adoucisseur_BWT PRO L 50 MAX:20 m³/h</t>
+  </si>
+  <si>
+    <t>Adoucisseurs</t>
+  </si>
+  <si>
+    <t>Citerne</t>
+  </si>
+  <si>
+    <t>CVC_EQE_Ballon de stockage ECS_Atlantic Corhydro:900 L TDH - jaquette souple M1 100 mm</t>
+  </si>
+  <si>
+    <t>Ballon ECS</t>
+  </si>
+  <si>
     <t>Contrôleur de Flux</t>
   </si>
   <si>
-    <t>CVC_ACA_Robinet de réglage droit:DN22 - 1208A03</t>
-  </si>
-  <si>
-    <t>DN22 - 1208A03</t>
+    <t>CVC_ACA_Clapet anti-retour taraudé:FF - DN15 à DN50</t>
+  </si>
+  <si>
+    <t>FF - DN15 à DN50</t>
   </si>
   <si>
     <t>IfcFlowController</t>
   </si>
   <si>
-    <t>22_Appareils Sanitaires</t>
-  </si>
-  <si>
-    <t>CVC_ACA_Vanne 2 voies motorisée:Standard</t>
+    <t>Vannes</t>
+  </si>
+  <si>
+    <t>CVC_ACA_Clapet anti-retour_Caleffi 561:561402A</t>
+  </si>
+  <si>
+    <t>561402A</t>
+  </si>
+  <si>
+    <t>CVC_ACA_Purgeur automatique_Flamco Flexvent:G3/8</t>
+  </si>
+  <si>
+    <t>G3/8</t>
+  </si>
+  <si>
+    <t>CVC_ACA_Purgeur d'air:DN25</t>
+  </si>
+  <si>
+    <t>DN25</t>
+  </si>
+  <si>
+    <t>CVC_ACA_Robinet de réglage droit:1208A03 - DN22</t>
+  </si>
+  <si>
+    <t>1208A03 - DN22</t>
+  </si>
+  <si>
+    <t>CVC_ACA_Soupape de sécurité:Standard</t>
   </si>
   <si>
     <t>Standard</t>
   </si>
   <si>
-    <t>21_Vannes</t>
+    <t>CVC_ACA_Soupape de sécurité_Caleffi:DN15 à DN32</t>
+  </si>
+  <si>
+    <t>DN15 à DN32</t>
+  </si>
+  <si>
+    <t>CVC_ACA_Vanne 2 voies PIBCV_Schneider VP228:VP228E-15BQS - DN15</t>
+  </si>
+  <si>
+    <t>VP228E-15BQS - DN15</t>
   </si>
   <si>
     <t>CVC_ACA_Vanne 3 voies:DN25</t>
   </si>
   <si>
-    <t>DN25</t>
-  </si>
-  <si>
     <t>CVC_ACA_Vanne 3 voies:DN32</t>
   </si>
   <si>
@@ -119,88 +197,82 @@
     <t>CVC_ACA_Vanne d'arrêt:Standard</t>
   </si>
   <si>
-    <t>CVC_ACA_Vanne de réglage:Standard</t>
-  </si>
-  <si>
-    <t>CVC_ACA_Vanne de réglage_IMI TA:Filetée</t>
-  </si>
-  <si>
-    <t>Filetée</t>
-  </si>
-  <si>
-    <t>CVC_ACA_Vanne motorisée:DN25</t>
-  </si>
-  <si>
-    <t>CVC_ACA_Vanne à boisseau sphérique avec raccord MF:Standard - col court</t>
-  </si>
-  <si>
-    <t>Standard - col court</t>
+    <t>CVC_ACA_Vanne d'équilibrage_IMI TA:DN32</t>
+  </si>
+  <si>
+    <t>CVC_ACA_Vanne à boisseau sphérique avec raccord MF:Col court</t>
+  </si>
+  <si>
+    <t>Col court</t>
   </si>
   <si>
     <t>CVC_ACA_Vanne à boisseau sphérique:Standard</t>
   </si>
   <si>
-    <t>CVC_AGA_Registre circulaire motorisé:Standard</t>
-  </si>
-  <si>
-    <t>07_Accessoires de gaines</t>
-  </si>
-  <si>
-    <t>CVS_ACA_CIRC_VanneArret:Standard</t>
-  </si>
-  <si>
-    <t>CVS_Registre_Circulaire_Motorisé:Équilibrage motorisé</t>
-  </si>
-  <si>
-    <t>Équilibrage motorisé</t>
-  </si>
-  <si>
-    <t>PLB_VAN_Vanne d’arrêt circulaire:Standard</t>
-  </si>
-  <si>
-    <t>PLB_VAN_Vanne d’arrêt:Standard</t>
-  </si>
-  <si>
-    <t>PLB_VAN_Vanne nourrice / clarinette aller:DN 15</t>
+    <t>CVC_AGA_Régulateur VAV circulaire_France Air Opti Drive:Opti Drive Modbus - DN selon instance</t>
+  </si>
+  <si>
+    <t>Opti Drive Modbus - DN selon instance</t>
+  </si>
+  <si>
+    <t>CVC_CAR_CLAPET_ANTI-RETOUR_TARAUDÉ:DN10 à DN100</t>
+  </si>
+  <si>
+    <t>DN10 à DN100</t>
+  </si>
+  <si>
+    <t>CVS_ACA_CIRC_Vanne reglage:DN selon instance</t>
+  </si>
+  <si>
+    <t>DN selon instance</t>
+  </si>
+  <si>
+    <t>CVS_ACA_CIRC_VanneArret:DN selon instance</t>
+  </si>
+  <si>
+    <t>CVS_Registre_Circulaire_Motorisé:Opti Drive Modbus - équilibrage motorisé</t>
+  </si>
+  <si>
+    <t>Opti Drive Modbus - équilibrage motorisé</t>
+  </si>
+  <si>
+    <t>PLB_ACA_Nourrice / clarinette aller:DN 15</t>
   </si>
   <si>
     <t>DN 15</t>
   </si>
   <si>
+    <t>PLB_ACA_Robinet à boisseau sphérique:NF</t>
+  </si>
+  <si>
+    <t>NF</t>
+  </si>
+  <si>
+    <t>PLB_ACA_Robinet à boisseau sphérique:NO</t>
+  </si>
+  <si>
+    <t>NO</t>
+  </si>
+  <si>
     <t>Convertisseur d’énergie</t>
   </si>
   <si>
-    <t>CVC_ACA_Compteur:Eau</t>
-  </si>
-  <si>
-    <t>Eau</t>
+    <t>CVC_AGA_Batterie eau chaude_Systemair Geniox Go 12:GXH-12 - 6,36 kW - eau 80/60°C</t>
+  </si>
+  <si>
+    <t>GXH-12 - 6,36 kW - eau 80/60°C</t>
   </si>
   <si>
     <t>IfcEnergyConversionDevice</t>
   </si>
   <si>
-    <t>17_Compteurs</t>
-  </si>
-  <si>
-    <t>CVC_ACA_Compteur:Énergie</t>
-  </si>
-  <si>
-    <t>Énergie</t>
-  </si>
-  <si>
-    <t>CVC_AGA_Batterie eau chaude_CTA:Standard</t>
-  </si>
-  <si>
-    <t>100_Hors TND</t>
-  </si>
-  <si>
-    <t>CVC_EQH_Échangeur à plaques_Alfa Laval TL3-BFG:40 kW - 25 plaques</t>
-  </si>
-  <si>
-    <t>40 kW - 25 plaques</t>
-  </si>
-  <si>
-    <t>18_Echangeurs</t>
+    <t>HVAC_Heat-Exchanger_Alfa-Laval_Alfa-Laval-TL3_ASME:40 kW - 25 plaques - ALLOY 304 - NBRB</t>
+  </si>
+  <si>
+    <t>40 kW - 25 plaques - ALLOY 304 - NBRB</t>
+  </si>
+  <si>
+    <t>Echangeurs</t>
   </si>
   <si>
     <t>Dalle</t>
@@ -215,424 +287,763 @@
     <t>IfcSlab</t>
   </si>
   <si>
-    <t>Luminaire</t>
-  </si>
-  <si>
-    <t>ELE_LUM_Luminaire rectangulaire:Type 1</t>
-  </si>
-  <si>
-    <t>Type 1</t>
+    <t>Débitmètre</t>
+  </si>
+  <si>
+    <t>CVC_ACA_Compteur d'énergie_Belimo EPIV:DN32</t>
+  </si>
+  <si>
+    <t>Compteurs</t>
+  </si>
+  <si>
+    <t>CVC_ACA_Compteur d'énergie_Belimo EPIV:DN50</t>
+  </si>
+  <si>
+    <t>DN50</t>
+  </si>
+  <si>
+    <t>CVC_ACA_Compteur d'énergie_Sharky 775:Sharky 775 - DN25</t>
+  </si>
+  <si>
+    <t>Sharky 775 - DN25</t>
+  </si>
+  <si>
+    <t>CVC_ACA_Compteur d'énergie_Sharky 775:Sharky 775 - DN32</t>
+  </si>
+  <si>
+    <t>Sharky 775 - DN32</t>
+  </si>
+  <si>
+    <t>PLB_ACA_Compteur d'eau_Sharky 775:Sharky 775 - DN15</t>
+  </si>
+  <si>
+    <t>Sharky 775 - DN15</t>
+  </si>
+  <si>
+    <t>Echangeur d’Air</t>
+  </si>
+  <si>
+    <t>CVC_EQE_Préparateur ECS_Atlantic Rubis Evo:SI 206 DD</t>
+  </si>
+  <si>
+    <t>SI 206 DD</t>
+  </si>
+  <si>
+    <t>Filtre</t>
+  </si>
+  <si>
+    <t>Filtre à tamis:DN selon instance</t>
+  </si>
+  <si>
+    <t>PLB_ACA_Filtre à tamis:DN32</t>
+  </si>
+  <si>
+    <t>Mobilier</t>
+  </si>
+  <si>
+    <t>PLB_EQA_Barre de relevage coudée:400 x 400 mm</t>
+  </si>
+  <si>
+    <t>IfcFurnishingElement</t>
+  </si>
+  <si>
+    <t>Appareils Sanitaires</t>
+  </si>
+  <si>
+    <t>Objet</t>
+  </si>
+  <si>
+    <t>CVC_AGA_Costière d'étanchéité circulaire:Standard</t>
+  </si>
+  <si>
+    <t>IfcBuildingElementProxy</t>
+  </si>
+  <si>
+    <t>CVC_AGA_Costière d’étanchéité circulaire:Standard</t>
+  </si>
+  <si>
+    <t>GEN_REP_Balise de géoréférencement:25</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>Non classé</t>
+  </si>
+  <si>
+    <t>Ouverture</t>
+  </si>
+  <si>
+    <t>CVC_RSV_Réservation circulaire:Face H</t>
+  </si>
+  <si>
+    <t>Face H</t>
+  </si>
+  <si>
+    <t>IfcOpeningElement</t>
+  </si>
+  <si>
+    <t>CVC_RSV_Réservation circulaire:Face V</t>
+  </si>
+  <si>
+    <t>Face V</t>
+  </si>
+  <si>
+    <t>CVC_RSV_Réservation rectangulaire:Face V</t>
+  </si>
+  <si>
+    <t>CVC_EQH_Circulateur simple_Grundfos MAGNA3:MAGNA3 25-40 N - 97924336</t>
+  </si>
+  <si>
+    <t>Raccord Tuyau</t>
+  </si>
+  <si>
+    <t>CVC_RAC_CAN_Acier noir_Bouchon:Standard</t>
+  </si>
+  <si>
+    <t>IfcFlowFitting</t>
+  </si>
+  <si>
+    <t>Raccords de Canalisations / Tuyauteries</t>
+  </si>
+  <si>
+    <t>CVC_RAC_CAN_Acier noir_Coude:Courbure 3D</t>
+  </si>
+  <si>
+    <t>Courbure 3D</t>
+  </si>
+  <si>
+    <t>CVC_RAC_CAN_Acier noir_Croix:Standard</t>
+  </si>
+  <si>
+    <t>CVC_RAC_CAN_Acier noir_Piquage:Longueur 25 mm</t>
+  </si>
+  <si>
+    <t>Longueur 25 mm</t>
+  </si>
+  <si>
+    <t>CVC_RAC_CAN_Acier noir_Réduction:Longueur x3</t>
+  </si>
+  <si>
+    <t>Longueur x3</t>
+  </si>
+  <si>
+    <t>CVC_RAC_CAN_Acier noir_Réduction:Longueur x4</t>
+  </si>
+  <si>
+    <t>Longueur x4</t>
+  </si>
+  <si>
+    <t>CVC_RAC_CAN_Acier noir_Té:Standard</t>
+  </si>
+  <si>
+    <t>Coude PVC FF:EU / EV / EP</t>
+  </si>
+  <si>
+    <t>EU / EV / EP</t>
+  </si>
+  <si>
+    <t>PLB_RAC_Bouchon cuivre Sudo:Standard</t>
+  </si>
+  <si>
+    <t>PLB_RAC_Bouchon inox à sertir:Ø15 à Ø108</t>
+  </si>
+  <si>
+    <t>Ø15 à Ø108</t>
+  </si>
+  <si>
+    <t>PLB_RAC_Bouchon inox à sertir:Ø15-108</t>
+  </si>
+  <si>
+    <t>Ø15-108</t>
+  </si>
+  <si>
+    <t>PLB_RAC_Coude PVC FF:Standard</t>
+  </si>
+  <si>
+    <t>PLB_RAC_Coude cintré cuivre:Standard</t>
+  </si>
+  <si>
+    <t>PLB_RAC_Coude cuivre Sudo:Standard</t>
+  </si>
+  <si>
+    <t>PLB_RAC_Coude inox à sertir:Ø15 à Ø108</t>
+  </si>
+  <si>
+    <t>PLB_RAC_Coude inox à sertir:Ø15-108</t>
+  </si>
+  <si>
+    <t>PLB_RAC_Coude inox:EN ISO 1127 - courbure 3D</t>
+  </si>
+  <si>
+    <t>EN ISO 1127 - courbure 3D</t>
+  </si>
+  <si>
+    <t>PLB_RAC_Coude inox:Norme EN ISO 1127 Courbure = 3D</t>
+  </si>
+  <si>
+    <t>Norme EN ISO 1127 Courbure = 3D</t>
+  </si>
+  <si>
+    <t>PLB_RAC_Culotte PVC 45° + coude 45° MF:EU / EV / EP</t>
+  </si>
+  <si>
+    <t>PLB_RAC_Réduction PVC:EU / EV / EP</t>
+  </si>
+  <si>
+    <t>PLB_RAC_Réduction cuivre Sudo:Standard</t>
+  </si>
+  <si>
+    <t>PLB_RAC_Réduction générique:Standard</t>
+  </si>
+  <si>
+    <t>PLB_RAC_Réduction inox à sertir:Ø15-108</t>
+  </si>
+  <si>
+    <t>PLB_RAC_Réduction inox:EN ISO 1127 - longueur x3</t>
+  </si>
+  <si>
+    <t>EN ISO 1127 - longueur x3</t>
+  </si>
+  <si>
+    <t>PLB_RAC_Réduction inox:Longueur x3 EN ISO 1127</t>
+  </si>
+  <si>
+    <t>Longueur x3 EN ISO 1127</t>
+  </si>
+  <si>
+    <t>PLB_RAC_Tampon PVC:EU / EV / EP</t>
+  </si>
+  <si>
+    <t>PLB_RAC_Té cuivre Sudo:Standard</t>
+  </si>
+  <si>
+    <t>PLB_RAC_Té inox à sertir:Ø15 à Ø108</t>
+  </si>
+  <si>
+    <t>PLB_RAC_Té inox à sertir:Ø15-108</t>
+  </si>
+  <si>
+    <t>PLB_RAC_Té inox:EN ISO 1127</t>
+  </si>
+  <si>
+    <t>EN ISO 1127</t>
+  </si>
+  <si>
+    <t>PLB_RAC_Union inox à sertir:Ø15-108</t>
+  </si>
+  <si>
+    <t>RAC CAN PVC Tampon:Standard</t>
+  </si>
+  <si>
+    <t>Réduction Cuivre SUDO:Standard</t>
+  </si>
+  <si>
+    <t>Raccords Flux</t>
+  </si>
+  <si>
+    <t>CVC_ACA_Manchon antivibratile_Sferaco:DN32 - avec brides</t>
+  </si>
+  <si>
+    <t>DN32 - avec brides</t>
+  </si>
+  <si>
+    <t>CVC_AGA_Manchette souple rectangulaire:Standard</t>
+  </si>
+  <si>
+    <t>Raccords de Gaines</t>
+  </si>
+  <si>
+    <t>CVC_AGA_Trappe de visite gaine circulaire dessous:200x100 mm</t>
+  </si>
+  <si>
+    <t>200x100 mm</t>
+  </si>
+  <si>
+    <t>Gaines</t>
+  </si>
+  <si>
+    <t>CVC_AGA_Trappe de visite gaine circulaire:180x80 mm</t>
+  </si>
+  <si>
+    <t>180x80 mm</t>
+  </si>
+  <si>
+    <t>CVC_AGA_Trappe de visite gaine circulaire:200x100 mm</t>
+  </si>
+  <si>
+    <t>CVC_AGA_Trappe de visite gaine rectangulaire dessous:200x100 mm</t>
+  </si>
+  <si>
+    <t>CVC_RAC_CAN_Acier_Manchon:Standard</t>
+  </si>
+  <si>
+    <t>CVC_RAC_CAN_Acier_Réduction:Longueur x3</t>
+  </si>
+  <si>
+    <t>CVC_RAC_CAN_Inox à sertir_Coude:Ø15 à Ø108</t>
+  </si>
+  <si>
+    <t>CVC_RAC_CAN_Inox à sertir_Réduction:Ø15 à Ø108</t>
+  </si>
+  <si>
+    <t>CVC_RAC_CAN_Inox à sertir_Té:Ø15 à Ø108</t>
+  </si>
+  <si>
+    <t>CVC_RAC_CAN_Réduction:Standard</t>
+  </si>
+  <si>
+    <t>CVC_RAC_GAI_Bouchon rectangulaire:Alu</t>
+  </si>
+  <si>
+    <t>Alu</t>
+  </si>
+  <si>
+    <t>CVC_RAC_GAI_Coude circulaire embouti:Courbure 1D</t>
+  </si>
+  <si>
+    <t>Courbure 1D</t>
+  </si>
+  <si>
+    <t>CVC_RAC_GAI_Coude circulaire segmenté:3 segments</t>
+  </si>
+  <si>
+    <t>3 segments</t>
+  </si>
+  <si>
+    <t>CVC_RAC_GAI_Coude circulaire:Galva</t>
+  </si>
+  <si>
+    <t>Galva</t>
+  </si>
+  <si>
+    <t>CVC_RAC_GAI_Coude rectangulaire joint coulissant:R120 - Alu</t>
+  </si>
+  <si>
+    <t>R120 - Alu</t>
+  </si>
+  <si>
+    <t>CVC_RAC_GAI_Coude rectangulaire rayon constant à bride:Rayon 100 mm</t>
+  </si>
+  <si>
+    <t>Rayon 100 mm</t>
+  </si>
+  <si>
+    <t>CVC_RAC_GAI_Coude rectangulaire rayon:Rayon 150 mm</t>
+  </si>
+  <si>
+    <t>Rayon 150 mm</t>
+  </si>
+  <si>
+    <t>CVC_RAC_GAI_Piquage circulaire:Longueur 30 mm</t>
+  </si>
+  <si>
+    <t>Longueur 30 mm</t>
+  </si>
+  <si>
+    <t>CVC_RAC_GAI_Piquage rectangulaire:Longueur 30 mm</t>
+  </si>
+  <si>
+    <t>CVC_RAC_GAI_Réduction rectangulaire concentrique:Angle 45°</t>
+  </si>
+  <si>
+    <t>Angle 45°</t>
+  </si>
+  <si>
+    <t>CVC_RAC_GAI_Sortie toiture_Sifflet grillagé:Ø125</t>
+  </si>
+  <si>
+    <t>Ø125</t>
+  </si>
+  <si>
+    <t>CVC_RAC_GAI_Sortie toiture_Sifflet grillagé:Ø200</t>
+  </si>
+  <si>
+    <t>Ø200</t>
+  </si>
+  <si>
+    <t>CVC_RAC_GAI_Sortie toiture_Sifflet grillagé:Ø500</t>
+  </si>
+  <si>
+    <t>Ø500</t>
+  </si>
+  <si>
+    <t>CVC_RAC_GAI_Transformation circulaire joint coulissant:Galva</t>
+  </si>
+  <si>
+    <t>CVC_RAC_GAI_Transformation rectangulaire à bride:Galva</t>
+  </si>
+  <si>
+    <t>CVC_RAC_GAI_Transformation rectangulaire-circulaire concentrique:Galva</t>
+  </si>
+  <si>
+    <t>CVC_RAC_GAI_Transformation ronde coulissante:Standard</t>
+  </si>
+  <si>
+    <t>CVC_RAC_GAI_Trappe de visite rectangulaire:200x100 mm</t>
+  </si>
+  <si>
+    <t>CVC_RAC_GAI_Té circulaire 90°:Standard</t>
+  </si>
+  <si>
+    <t>CVC_RAC_GAI_Té souche insonorisé_Cairox TSIJ:Ø125</t>
+  </si>
+  <si>
+    <t>CVC_RAC_GAI_Té souche insonorisé_Cairox TSIJ:Ø200</t>
+  </si>
+  <si>
+    <t>CVC_RAC_GAI_Té souche insonorisé_Cairox TSIJ:Ø500</t>
+  </si>
+  <si>
+    <t>CVC_RAC_GAI_Union circulaire femelle:Standard</t>
+  </si>
+  <si>
+    <t>CVC_RAC_GAI_Union rectangulaire coulissante:Standard</t>
+  </si>
+  <si>
+    <t>CVC_RAC_GAI_Union rectangulaire mâle:Standard</t>
+  </si>
+  <si>
+    <t>PLB_INOX_A_SERTIR_TE1:Ø15 à Ø108</t>
+  </si>
+  <si>
+    <t>RAC_GAI_CIRC_Coude Segmenté:3 segments</t>
+  </si>
+  <si>
+    <t>RAC_GAI_CIRC_Piquage:Longueur 30 mm</t>
+  </si>
+  <si>
+    <t>RAC_GAI_MULT_Transformation_Rectangulaire-Circulaire_Concentrique:Standard</t>
+  </si>
+  <si>
+    <t>Raccord Union Male Gaine Rectangulaire:Standard</t>
+  </si>
+  <si>
+    <t>Transformation RE Bride:Standard</t>
+  </si>
+  <si>
+    <t>Revêtement</t>
+  </si>
+  <si>
+    <t>Isolation des canalisations:EBC Armaflex (XG)</t>
+  </si>
+  <si>
+    <t>EBC Armaflex (XG)</t>
+  </si>
+  <si>
+    <t>IfcCovering</t>
+  </si>
+  <si>
+    <t>Isolants</t>
+  </si>
+  <si>
+    <t>Isolation des canalisations:EBC Laine de roche ALU KRAFT</t>
+  </si>
+  <si>
+    <t>EBC Laine de roche ALU KRAFT</t>
+  </si>
+  <si>
+    <t>Isolation des canalisations:EBC Laine de roche PVC KRAFT</t>
+  </si>
+  <si>
+    <t>EBC Laine de roche PVC KRAFT</t>
+  </si>
+  <si>
+    <t>Isolation des canalisations:ISO_THE_Laine Minérale + PVC</t>
+  </si>
+  <si>
+    <t>ISO_THE_Laine Minérale + PVC</t>
+  </si>
+  <si>
+    <t>Isolation des canalisations:Isolation thermique Armaflex</t>
+  </si>
+  <si>
+    <t>Isolation thermique Armaflex</t>
+  </si>
+  <si>
+    <t>Isolation des canalisations:Laine de roche + Alu Kraft</t>
+  </si>
+  <si>
+    <t>Laine de roche + Alu Kraft</t>
+  </si>
+  <si>
+    <t>Isolation des canalisations:Laine de roche + PVC Kraft</t>
+  </si>
+  <si>
+    <t>Laine de roche + PVC Kraft</t>
+  </si>
+  <si>
+    <t>Isolation des gaines:ISO_THE_Laine Minérale + Alu</t>
+  </si>
+  <si>
+    <t>ISO_THE_Laine Minérale + Alu</t>
+  </si>
+  <si>
+    <t>Segment de flux</t>
+  </si>
+  <si>
+    <t>Canalisation souple arrondie:CAN_Souple</t>
+  </si>
+  <si>
+    <t>CAN_Souple</t>
+  </si>
+  <si>
+    <t>IfcFlowSegment</t>
+  </si>
+  <si>
+    <t>Canalisations / Tuyauteries</t>
+  </si>
+  <si>
+    <t>Canalisation:CAN_Acier T10_Piquage-Coude 3D</t>
+  </si>
+  <si>
+    <t>CAN_Acier T10_Piquage-Coude 3D</t>
+  </si>
+  <si>
+    <t>Canalisation:CAN_Acier T10_Té-Coude 3D</t>
+  </si>
+  <si>
+    <t>CAN_Acier T10_Té-Coude 3D</t>
+  </si>
+  <si>
+    <t>Canalisation:CAN_Acier T3_Piquage-Coude 3D</t>
+  </si>
+  <si>
+    <t>CAN_Acier T3_Piquage-Coude 3D</t>
+  </si>
+  <si>
+    <t>Canalisation:CAN_Acier T3_Té-Coude 3D</t>
+  </si>
+  <si>
+    <t>CAN_Acier T3_Té-Coude 3D</t>
+  </si>
+  <si>
+    <t>Canalisation:PLB_INOX_A_SERTIR</t>
+  </si>
+  <si>
+    <t>PLB_INOX_A_SERTIR</t>
+  </si>
+  <si>
+    <t>Canalisation:PLB_INOX_A_SERTIR 304L</t>
+  </si>
+  <si>
+    <t>PLB_INOX_A_SERTIR 304L</t>
+  </si>
+  <si>
+    <t>Gaine circulaire:CVC_TÔLE_GALVA_PIQUAGE</t>
+  </si>
+  <si>
+    <t>CVC_TÔLE_GALVA_PIQUAGE</t>
+  </si>
+  <si>
+    <t>Gaine circulaire:EBC Raccord avec té et coude lisse</t>
+  </si>
+  <si>
+    <t>EBC Raccord avec té et coude lisse</t>
+  </si>
+  <si>
+    <t>Gaine circulaire:EBC Raccord par piquage et coude lisse</t>
+  </si>
+  <si>
+    <t>EBC Raccord par piquage et coude lisse</t>
+  </si>
+  <si>
+    <t>Gaine circulaire:EBC Reduction excentree / Coude segments</t>
+  </si>
+  <si>
+    <t>EBC Reduction excentree / Coude segments</t>
+  </si>
+  <si>
+    <t>Gaine circulaire:GAI_CIRC_Piquage_Coude lisse</t>
+  </si>
+  <si>
+    <t>GAI_CIRC_Piquage_Coude lisse</t>
+  </si>
+  <si>
+    <t>Gaine circulaire:GAI_CIRC_Piquage_Coude segmenté</t>
+  </si>
+  <si>
+    <t>GAI_CIRC_Piquage_Coude segmenté</t>
+  </si>
+  <si>
+    <t>Gaine flexible circulaire:GAI_CIRC_Souple</t>
+  </si>
+  <si>
+    <t>GAI_CIRC_Souple</t>
+  </si>
+  <si>
+    <t>Gaine rectangulaire:CVC_TÔLE_ALU_PIQUAGE_ET_COUDE_A_RAYON</t>
+  </si>
+  <si>
+    <t>CVC_TÔLE_ALU_PIQUAGE_ET_COUDE_A_RAYON</t>
+  </si>
+  <si>
+    <t>Gaine rectangulaire:CVC_TÔLE_GALVA_PIQUAGE_ET_COUDE_A_RAYON</t>
+  </si>
+  <si>
+    <t>CVC_TÔLE_GALVA_PIQUAGE_ET_COUDE_A_RAYON</t>
+  </si>
+  <si>
+    <t>Gaine rectangulaire:EBC Raccord par piquage et coude à rayon</t>
+  </si>
+  <si>
+    <t>EBC Raccord par piquage et coude à rayon</t>
+  </si>
+  <si>
+    <t>Gaine rectangulaire:GAI_RECT_Piquage_Coude à rayon</t>
+  </si>
+  <si>
+    <t>GAI_RECT_Piquage_Coude à rayon</t>
+  </si>
+  <si>
+    <t>Silencieux Conduit</t>
+  </si>
+  <si>
+    <t>CVC_AGA_Piège à son circulaire:L=600 mm</t>
+  </si>
+  <si>
+    <t>CVC_AGA_Piège à son rectangulaire:L=1000 mm</t>
+  </si>
+  <si>
+    <t>CVC_AGA_Piège à son rectangulaire:L=600 mm</t>
+  </si>
+  <si>
+    <t>Terminaison Flux</t>
+  </si>
+  <si>
+    <t>CVC_BOU_Bouche circulaire_France Air BSC:BSC Ø125 - reprise/soufflage</t>
+  </si>
+  <si>
+    <t>BSC Ø125 - reprise/soufflage</t>
   </si>
   <si>
     <t>IfcFlowTerminal</t>
   </si>
   <si>
-    <t>Objet</t>
-  </si>
-  <si>
-    <t>CVC_AGA_Costière d'étanchéité circulaire:Standard</t>
-  </si>
-  <si>
-    <t>IfcBuildingElementProxy</t>
-  </si>
-  <si>
-    <t>CVC_RSV_Réservation circulaire:Face H</t>
-  </si>
-  <si>
-    <t>Face H</t>
-  </si>
-  <si>
-    <t>CVC_RSV_Réservation circulaire:Face V</t>
-  </si>
-  <si>
-    <t>Face V</t>
-  </si>
-  <si>
-    <t>CVC_RSV_Réservation rectangulaire:Face V</t>
-  </si>
-  <si>
-    <t>GEN_REP_Balise de géoréférencement:25</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>Non classé</t>
-  </si>
-  <si>
-    <t>Raccord Tuyau</t>
-  </si>
-  <si>
-    <t>PLB_RAC_Coude inox à sertir:Ø15-108</t>
-  </si>
-  <si>
-    <t>Ø15-108</t>
-  </si>
-  <si>
-    <t>IfcFlowFitting</t>
-  </si>
-  <si>
-    <t>03_Raccords de Canalisations / Tuyauteries</t>
-  </si>
-  <si>
-    <t>PLB_RAC_Té inox à sertir:Ø15-108</t>
-  </si>
-  <si>
-    <t>Raccords Flux</t>
-  </si>
-  <si>
-    <t>CVC_AGA_Manchette souple rectangulaire:Standard</t>
-  </si>
-  <si>
-    <t>06_Raccords de Gaines</t>
-  </si>
-  <si>
-    <t>CVC_AGA_Trappe de visite gaine circulaire dessous:200x100 mm</t>
-  </si>
-  <si>
-    <t>200x100 mm</t>
-  </si>
-  <si>
-    <t>05_Gaines</t>
-  </si>
-  <si>
-    <t>CVC_AGA_Trappe de visite gaine circulaire:180x80 mm</t>
-  </si>
-  <si>
-    <t>180x80 mm</t>
-  </si>
-  <si>
-    <t>CVC_AGA_Trappe de visite gaine circulaire:200x100 mm</t>
-  </si>
-  <si>
-    <t>CVC_AGA_Trappe de visite gaine rectangulaire dessous:200x100 mm</t>
-  </si>
-  <si>
-    <t>CVC_RAC_CAN_Acier inox_Coude:EN ISO 1127 - courbure 3D</t>
-  </si>
-  <si>
-    <t>EN ISO 1127 - courbure 3D</t>
-  </si>
-  <si>
-    <t>CVC_RAC_CAN_Acier inox_Réduction:EN ISO 1127 - longueur x3</t>
-  </si>
-  <si>
-    <t>EN ISO 1127 - longueur x3</t>
-  </si>
-  <si>
-    <t>CVC_RAC_CAN_Acier inox_Té:EN ISO 1127</t>
-  </si>
-  <si>
-    <t>EN ISO 1127</t>
-  </si>
-  <si>
-    <t>CVC_RAC_CAN_Acier noir_Bouchon:Standard</t>
-  </si>
-  <si>
-    <t>CVC_RAC_CAN_Acier noir_Coude:Courbure 3D</t>
-  </si>
-  <si>
-    <t>Courbure 3D</t>
-  </si>
-  <si>
-    <t>CVC_RAC_CAN_Acier noir_Croix:Standard</t>
-  </si>
-  <si>
-    <t>CVC_RAC_CAN_Acier noir_Piquage droit:Longueur 25 mm</t>
-  </si>
-  <si>
-    <t>Longueur 25 mm</t>
-  </si>
-  <si>
-    <t>CVC_RAC_CAN_Acier noir_Piquage:Longueur 25 mm</t>
-  </si>
-  <si>
-    <t>CVC_RAC_CAN_Acier noir_Réduction:Longueur x3</t>
-  </si>
-  <si>
-    <t>Longueur x3</t>
-  </si>
-  <si>
-    <t>CVC_RAC_CAN_Acier noir_Té:Standard</t>
-  </si>
-  <si>
-    <t>CVC_RAC_CAN_Inox à sertir_Coude:Ø15-108</t>
-  </si>
-  <si>
-    <t>CVC_RAC_CAN_Inox à sertir_Réduction:Ø15-108</t>
-  </si>
-  <si>
-    <t>CVC_RAC_CAN_Inox à sertir_Té:Ø15-108</t>
-  </si>
-  <si>
-    <t>CVC_RAC_CAN_Manchon:Standard</t>
-  </si>
-  <si>
-    <t>CVC_RAC_CAN_Réduction:Standard</t>
-  </si>
-  <si>
-    <t>CVC_RAC_GAI_Bouchon rectangulaire:Alu</t>
-  </si>
-  <si>
-    <t>Alu</t>
-  </si>
-  <si>
-    <t>CVC_RAC_GAI_Coude circulaire embouti:Courbure 1D</t>
-  </si>
-  <si>
-    <t>Courbure 1D</t>
-  </si>
-  <si>
-    <t>CVC_RAC_GAI_Coude circulaire segmenté:3 segments</t>
-  </si>
-  <si>
-    <t>3 segments</t>
-  </si>
-  <si>
-    <t>CVC_RAC_GAI_Coude circulaire:Galva</t>
-  </si>
-  <si>
-    <t>Galva</t>
-  </si>
-  <si>
-    <t>CVC_RAC_GAI_Coude rectangulaire joint coulissant:R120 - Alu</t>
-  </si>
-  <si>
-    <t>R120 - Alu</t>
-  </si>
-  <si>
-    <t>CVC_RAC_GAI_Coude rectangulaire rayon constant à bride:Rayon 100 mm</t>
-  </si>
-  <si>
-    <t>Rayon 100 mm</t>
-  </si>
-  <si>
-    <t>CVC_RAC_GAI_Coude rectangulaire rayon:Rayon 150 mm</t>
-  </si>
-  <si>
-    <t>Rayon 150 mm</t>
-  </si>
-  <si>
-    <t>CVC_RAC_GAI_Piquage circulaire:Longueur 30 mm</t>
-  </si>
-  <si>
-    <t>Longueur 30 mm</t>
-  </si>
-  <si>
-    <t>CVC_RAC_GAI_Piquage rectangulaire:Longueur 30 mm</t>
-  </si>
-  <si>
-    <t>CVC_RAC_GAI_Réduction rectangulaire concentrique:Angle 45°</t>
-  </si>
-  <si>
-    <t>Angle 45°</t>
-  </si>
-  <si>
-    <t>CVC_RAC_GAI_Sifflet grillagé:Ø125</t>
-  </si>
-  <si>
-    <t>Ø125</t>
-  </si>
-  <si>
-    <t>CVC_RAC_GAI_Sifflet grillagé:Ø200</t>
-  </si>
-  <si>
-    <t>Ø200</t>
-  </si>
-  <si>
-    <t>CVC_RAC_GAI_Sifflet grillagé:Ø500</t>
-  </si>
-  <si>
-    <t>Ø500</t>
-  </si>
-  <si>
-    <t>CVC_RAC_GAI_Transformation circulaire joint coulissant:Galva</t>
-  </si>
-  <si>
-    <t>CVC_RAC_GAI_Transformation rectangulaire à bride:Galva</t>
-  </si>
-  <si>
-    <t>CVC_RAC_GAI_Transformation rectangulaire-circulaire concentrique:Galva</t>
-  </si>
-  <si>
-    <t>CVC_RAC_GAI_Transformation ronde coulissante:Standard</t>
-  </si>
-  <si>
-    <t>CVC_RAC_GAI_Trappe de visite rectangulaire:200x100 mm</t>
-  </si>
-  <si>
-    <t>CVC_RAC_GAI_Té circulaire 90°:Standard</t>
-  </si>
-  <si>
-    <t>CVC_RAC_GAI_Té souche_Cairox TSIJ:Ø125</t>
-  </si>
-  <si>
-    <t>CVC_RAC_GAI_Té souche_Cairox TSIJ:Ø200</t>
-  </si>
-  <si>
-    <t>CVC_RAC_GAI_Té souche_Cairox TSIJ:Ø500</t>
-  </si>
-  <si>
-    <t>CVC_RAC_GAI_Union circulaire femelle:Standard</t>
-  </si>
-  <si>
-    <t>CVC_RAC_GAI_Union rectangulaire coulissante:Standard</t>
-  </si>
-  <si>
-    <t>CVC_RAC_GAI_Union rectangulaire mâle:Standard</t>
-  </si>
-  <si>
-    <t>Coude PVC FF:EU / EV / EP</t>
-  </si>
-  <si>
-    <t>EU / EV / EP</t>
-  </si>
-  <si>
-    <t>PLB_RAC_Bouchon inox à sertir:Ø15-108</t>
-  </si>
-  <si>
-    <t>PLB_RAC_Coude PVC FF:Standard</t>
-  </si>
-  <si>
-    <t>PLB_RAC_Coude cintré cuivre:Standard</t>
-  </si>
-  <si>
-    <t>PLB_RAC_Coude cuivre Sudo:Standard</t>
-  </si>
-  <si>
-    <t>PLB_RAC_Culotte PVC 45° + coude 45° MF:EU / EV / EP</t>
-  </si>
-  <si>
-    <t>PLB_RAC_Réduction cuivre Sudo:Standard</t>
-  </si>
-  <si>
-    <t>PLB_RAC_Réduction inox à sertir:Ø15-108</t>
-  </si>
-  <si>
-    <t>PLB_RAC_Réduction inox:Longueur x3 EN ISO 1127</t>
-  </si>
-  <si>
-    <t>Longueur x3 EN ISO 1127</t>
-  </si>
-  <si>
-    <t>PLB_RAC_Tampon PVC:EU / EV / EP</t>
-  </si>
-  <si>
-    <t>PLB_RAC_Té cuivre Sudo:Standard</t>
-  </si>
-  <si>
-    <t>PLB_RAC_Union inox à sertir:Ø15-108</t>
-  </si>
-  <si>
-    <t>RAC_GAI_CIRC_Coude Segmenté:3 segments</t>
-  </si>
-  <si>
-    <t>RAC_GAI_CIRC_Piquage:Longueur 30 mm</t>
-  </si>
-  <si>
-    <t>RAC_GAI_MULT_Transformation_Rectangulaire-Circulaire_Concentrique:Standard</t>
-  </si>
-  <si>
-    <t>Raccord Union Male Gaine Rectangulaire:Standard</t>
-  </si>
-  <si>
-    <t>Réduction Cuivre SUDO:Standard</t>
-  </si>
-  <si>
-    <t>Transformation RE Bride:Standard</t>
-  </si>
-  <si>
-    <t>Revêtement</t>
-  </si>
-  <si>
-    <t>Isolation des canalisations:EBC Armaflex (XG)</t>
-  </si>
-  <si>
-    <t>EBC Armaflex (XG)</t>
-  </si>
-  <si>
-    <t>IfcCovering</t>
-  </si>
-  <si>
-    <t>08_Isolants</t>
-  </si>
-  <si>
-    <t>Isolation des canalisations:EBC Laine de roche ALU KRAFT</t>
-  </si>
-  <si>
-    <t>EBC Laine de roche ALU KRAFT</t>
-  </si>
-  <si>
-    <t>Isolation des canalisations:EBC Laine de roche PVC KRAFT</t>
-  </si>
-  <si>
-    <t>EBC Laine de roche PVC KRAFT</t>
-  </si>
-  <si>
-    <t>Isolation des canalisations:ISO_THE_Laine Minérale + PVC</t>
-  </si>
-  <si>
-    <t>ISO_THE_Laine Minérale + PVC</t>
-  </si>
-  <si>
-    <t>Isolation des canalisations:Isolation thermique Armaflex</t>
-  </si>
-  <si>
-    <t>Isolation thermique Armaflex</t>
-  </si>
-  <si>
-    <t>Isolation des canalisations:Laine de roche + Alu Kraft</t>
-  </si>
-  <si>
-    <t>Laine de roche + Alu Kraft</t>
-  </si>
-  <si>
-    <t>Isolation des canalisations:Laine de roche + PVC Kraft</t>
-  </si>
-  <si>
-    <t>Laine de roche + PVC Kraft</t>
-  </si>
-  <si>
-    <t>Isolation des canalisations:Laine minérale + PVC</t>
-  </si>
-  <si>
-    <t>Laine minérale + PVC</t>
-  </si>
-  <si>
-    <t>Isolation des gaines:ISO_THE_Laine Minérale + Alu</t>
-  </si>
-  <si>
-    <t>ISO_THE_Laine Minérale + Alu</t>
-  </si>
-  <si>
-    <t>Segment de flux</t>
-  </si>
-  <si>
-    <t>CVC_AGA_Costière d’étanchéité circulaire:Standard</t>
-  </si>
-  <si>
-    <t>IfcFlowSegment</t>
-  </si>
-  <si>
-    <t>Canalisation souple arrondie:CAN_Souple</t>
-  </si>
-  <si>
-    <t>CAN_Souple</t>
-  </si>
-  <si>
-    <t>02_Canalisations / Tuyauteries</t>
-  </si>
-  <si>
-    <t>Canalisation:CAN_Acier T10_Piquage-Coude 3D</t>
-  </si>
-  <si>
-    <t>CAN_Acier T10_Piquage-Coude 3D</t>
-  </si>
-  <si>
-    <t>Canalisation:CAN_Acier T10_Té-Coude 3D</t>
-  </si>
-  <si>
-    <t>CAN_Acier T10_Té-Coude 3D</t>
+    <t>Diffuseur</t>
+  </si>
+  <si>
+    <t>CVC_BOU_Bouche double flux_France Air RAD Régul'Air 2:Reprise - débit constant réglable</t>
+  </si>
+  <si>
+    <t>Reprise - débit constant réglable</t>
+  </si>
+  <si>
+    <t>CVC_BOU_Bouche plafonnière de soufflage:Soufflage - débit constant réglable</t>
+  </si>
+  <si>
+    <t>Soufflage - débit constant réglable</t>
+  </si>
+  <si>
+    <t>CVC_BOU_Diffuseur basse vitesse_France Air GFF SP:GFF SP 3.6</t>
+  </si>
+  <si>
+    <t>GFF SP 3.6</t>
+  </si>
+  <si>
+    <t>CVC_BOU_Gaine perforée de soufflage_Klimagiel:Soufflage Ø300/Ø400 - RAL 9001 mat</t>
+  </si>
+  <si>
+    <t>Soufflage Ø300/Ø400 - RAL 9001 mat</t>
+  </si>
+  <si>
+    <t>CVC_BOU_Gaine perforée_Klimagiel Induction METALjet:Reprise Ø400 - RAL 9001 mat</t>
+  </si>
+  <si>
+    <t>Reprise Ø400 - RAL 9001 mat</t>
+  </si>
+  <si>
+    <t>CVC_TER_Panneau rayonnant_Sabiana Pulsar Acoustic Inox:P1 - 1195 mm - réf. 0086331 - RAL 9001</t>
+  </si>
+  <si>
+    <t>P1 - 1195 mm - réf. 0086331 - RAL 9001</t>
+  </si>
+  <si>
+    <t>CVC_TER_Panneau rayonnant_Sabiana Pulsar Acoustic Inox:P3 - 2395 mm - réf. 0086333 - RAL 9001</t>
+  </si>
+  <si>
+    <t>P3 - 2395 mm - réf. 0086333 - RAL 9001</t>
+  </si>
+  <si>
+    <t>CVC_TER_Radiateur_Finimetal Reggane 3010 Plan:Reggane 3010 Plan</t>
+  </si>
+  <si>
+    <t>Reggane 3010 Plan</t>
+  </si>
+  <si>
+    <t>Radiateurs</t>
+  </si>
+  <si>
+    <t>Terminal déchets</t>
+  </si>
+  <si>
+    <t>PLB_ACC_Siphon de sol horizontal:Standard</t>
+  </si>
+  <si>
+    <t>Terminal sanitaire</t>
+  </si>
+  <si>
+    <t>PBS 2b Lavabo PMR:Lavabo moulé + robinet PRESTO 4000S</t>
+  </si>
+  <si>
+    <t>Lavabo moulé + robinet PRESTO 4000S</t>
+  </si>
+  <si>
+    <t>PLB_ACC_Siphon sous lavabo:DN 40</t>
+  </si>
+  <si>
+    <t>DN 40</t>
+  </si>
+  <si>
+    <t>PLB_EQS_Lavabo PMR_Geberit Jerico + Presto:Lavabo moulé + robinet PRESTO NEO S 65200</t>
+  </si>
+  <si>
+    <t>Lavabo moulé + robinet PRESTO NEO S 65200</t>
+  </si>
+  <si>
+    <t>PLB_EQS_Panneau de douche_Porcher Prestotem:Prestotem 2 P50 MT - 88800</t>
+  </si>
+  <si>
+    <t>Prestotem 2 P50 MT - 88800</t>
+  </si>
+  <si>
+    <t>PLB_EQS_Urinoir_Porcher:285 x 295 x 415 mm</t>
+  </si>
+  <si>
+    <t>285 x 295 x 415 mm</t>
+  </si>
+  <si>
+    <t>PLB_EQS_Vidoir avec grille:455 x 390 x 355 mm</t>
+  </si>
+  <si>
+    <t>455 x 390 x 355 mm</t>
+  </si>
+  <si>
+    <t>PLB_EQS_WC suspendu PMR_Porcher Matura + Presto:Bâti-support 18460 + cuvette rallongée S303201</t>
+  </si>
+  <si>
+    <t>Bâti-support 18460 + cuvette rallongée S303201</t>
+  </si>
+  <si>
+    <t>PLB_EQS_WC suspendu_Porcher Matura + Presto:Bâti-support 18460 + cuvette R003001</t>
+  </si>
+  <si>
+    <t>Bâti-support 18460 + cuvette R003001</t>
+  </si>
+  <si>
+    <t>PLB_EQS_Évier granit:970 x 500 x 220 mm + mitigeur</t>
+  </si>
+  <si>
+    <t>970 x 500 x 220 mm + mitigeur</t>
+  </si>
+  <si>
+    <t>Tuyau</t>
+  </si>
+  <si>
+    <t>Canalisation:CAN_Acier-Inox_304L</t>
+  </si>
+  <si>
+    <t>CAN_Acier-Inox_304L</t>
   </si>
   <si>
     <t>Canalisation:CAN_Acier-Inox_Norme EN ISO 1127</t>
@@ -641,9 +1052,21 @@
     <t>CAN_Acier-Inox_Norme EN ISO 1127</t>
   </si>
   <si>
+    <t>Canalisation:EBC Acier Inox type SERTINOX</t>
+  </si>
+  <si>
+    <t>EBC Acier Inox type SERTINOX</t>
+  </si>
+  <si>
     <t>Canalisation:EU / EV / EP</t>
   </si>
   <si>
+    <t>Canalisation:EU / EV / EP 1</t>
+  </si>
+  <si>
+    <t>EU / EV / EP 1</t>
+  </si>
+  <si>
     <t>Canalisation:Inox</t>
   </si>
   <si>
@@ -656,280 +1079,94 @@
     <t>Inox 316L</t>
   </si>
   <si>
-    <t>Canalisation:PLB_INOX_A_SERTIR</t>
-  </si>
-  <si>
-    <t>PLB_INOX_A_SERTIR</t>
-  </si>
-  <si>
-    <t>Canalisation:PLB_INOX_A_SERTIR 304L</t>
-  </si>
-  <si>
-    <t>PLB_INOX_A_SERTIR 304L</t>
-  </si>
-  <si>
-    <t>Gaine circulaire:CVC_TÔLE_GALVA_PIQUAGE</t>
-  </si>
-  <si>
-    <t>CVC_TÔLE_GALVA_PIQUAGE</t>
-  </si>
-  <si>
-    <t>Gaine circulaire:EBC Raccord avec té et coude lisse</t>
-  </si>
-  <si>
-    <t>EBC Raccord avec té et coude lisse</t>
-  </si>
-  <si>
-    <t>Gaine circulaire:EBC Raccord par piquage et coude lisse</t>
-  </si>
-  <si>
-    <t>EBC Raccord par piquage et coude lisse</t>
-  </si>
-  <si>
-    <t>Gaine circulaire:EBC Reduction excentree / Coude segments</t>
-  </si>
-  <si>
-    <t>EBC Reduction excentree / Coude segments</t>
-  </si>
-  <si>
-    <t>Gaine circulaire:GAI_CIRC_Piquage_Coude lisse</t>
-  </si>
-  <si>
-    <t>GAI_CIRC_Piquage_Coude lisse</t>
-  </si>
-  <si>
-    <t>Gaine circulaire:GAI_CIRC_Piquage_Coude segmenté</t>
-  </si>
-  <si>
-    <t>GAI_CIRC_Piquage_Coude segmenté</t>
-  </si>
-  <si>
-    <t>Gaine flexible circulaire:GAI_CIRC_Souple</t>
-  </si>
-  <si>
-    <t>GAI_CIRC_Souple</t>
-  </si>
-  <si>
-    <t>Gaine rectangulaire:CVC_TÔLE_ALU_PIQUAGE_ET_COUDE_A_RAYON</t>
-  </si>
-  <si>
-    <t>CVC_TÔLE_ALU_PIQUAGE_ET_COUDE_A_RAYON</t>
-  </si>
-  <si>
-    <t>Gaine rectangulaire:CVC_TÔLE_GALVA_PIQUAGE_ET_COUDE_A_RAYON</t>
-  </si>
-  <si>
-    <t>CVC_TÔLE_GALVA_PIQUAGE_ET_COUDE_A_RAYON</t>
-  </si>
-  <si>
-    <t>Gaine rectangulaire:EBC Raccord par piquage et coude à rayon</t>
-  </si>
-  <si>
-    <t>EBC Raccord par piquage et coude à rayon</t>
-  </si>
-  <si>
-    <t>Gaine rectangulaire:GAI_RECT_Piquage_Coude à rayon</t>
-  </si>
-  <si>
-    <t>GAI_RECT_Piquage_Coude à rayon</t>
-  </si>
-  <si>
-    <t>PLB_INOX_A_SERTIR_TE1:Ø15-108</t>
-  </si>
-  <si>
-    <t>Silencieux Conduit</t>
-  </si>
-  <si>
-    <t>CVC_AGA_Piège à son circulaire:Longueur 600 mm</t>
-  </si>
-  <si>
-    <t>IfcFlowTreatmentDevice</t>
-  </si>
-  <si>
-    <t>CVC_AGA_Piège à son rectangulaire:Longueur 1000 mm</t>
-  </si>
-  <si>
-    <t>CVC_AGA_Piège à son rectangulaire:Longueur 600 mm</t>
-  </si>
-  <si>
-    <t>Terminaison Flux</t>
-  </si>
-  <si>
-    <t>CVC_BOU_Bouche circulaire reprise:Ø125</t>
-  </si>
-  <si>
-    <t>11_Diffuseur</t>
-  </si>
-  <si>
-    <t>CVC_BOU_Bouche plafonnière reprise:Standard</t>
-  </si>
-  <si>
-    <t>CVC_BOU_Bouche plafonnière soufflage:Standard</t>
-  </si>
-  <si>
-    <t>CVC_BOU_Diffuseur mural reprise_Swegon DRI250:590x1990 mm</t>
-  </si>
-  <si>
-    <t>590x1990 mm</t>
-  </si>
-  <si>
-    <t>CVC_BOU_Gaine perforée reprise_Klimagiel:Finition blanc laqué</t>
-  </si>
-  <si>
-    <t>Finition blanc laqué</t>
-  </si>
-  <si>
-    <t>CVC_BOU_Gaine perforée soufflage_Klimagiel:Finition blanc laqué</t>
-  </si>
-  <si>
-    <t>CVC_EQH_Panneau rayonnant_Sabiana Pulsar:Pulsar P.FE 1 - 600x1200 actif</t>
-  </si>
-  <si>
-    <t>Pulsar P.FE 1 - 600x1200 actif</t>
-  </si>
-  <si>
-    <t>CVC_EQH_Panneau rayonnant_Sabiana Pulsar:Pulsar P.FE 3 - 600x2400 actif</t>
-  </si>
-  <si>
-    <t>Pulsar P.FE 3 - 600x2400 actif</t>
-  </si>
-  <si>
-    <t>CVC_EQH_Radiateur_Finimetal Reggane Plan:Standard</t>
-  </si>
-  <si>
-    <t>14_Radiateurs</t>
-  </si>
-  <si>
-    <t>PBS 2b Lavabo PMR:Lavabo moulé + robinet PRESTO 4000S</t>
-  </si>
-  <si>
-    <t>Lavabo moulé + robinet PRESTO 4000S</t>
-  </si>
-  <si>
-    <t>PLB_ACC_Siphon de sol horizontal:Standard</t>
-  </si>
-  <si>
-    <t>PLB_ACC_Siphon sous lavabo:DN 40</t>
-  </si>
-  <si>
-    <t>DN 40</t>
-  </si>
-  <si>
-    <t>PLB_EQA_Barre de relevage coudée:400 x 400 mm</t>
-  </si>
-  <si>
-    <t>400 x 400 mm</t>
-  </si>
-  <si>
-    <t>PLB_EQS_Lavabo PMR_Geberit Jerico + Presto:Lavabo moulé + robinet PRESTO NEO S 65200</t>
-  </si>
-  <si>
-    <t>Lavabo moulé + robinet PRESTO NEO S 65200</t>
-  </si>
-  <si>
-    <t>PLB_EQS_Panneau de douche_Porcher Prestotem:Prestotem 2 P50 MT - 88800</t>
-  </si>
-  <si>
-    <t>Prestotem 2 P50 MT - 88800</t>
-  </si>
-  <si>
-    <t>PLB_EQS_Urinoir_Porcher:285 x 295 x 415 mm</t>
-  </si>
-  <si>
-    <t>285 x 295 x 415 mm</t>
-  </si>
-  <si>
-    <t>PLB_EQS_Vidoir avec grille:455 x 390 x 355 mm</t>
-  </si>
-  <si>
-    <t>455 x 390 x 355 mm</t>
-  </si>
-  <si>
-    <t>PLB_EQS_WC suspendu PMR_Porcher Matura + Presto:Bâti-support 18460 + cuvette rallongée S303201</t>
-  </si>
-  <si>
-    <t>Bâti-support 18460 + cuvette rallongée S303201</t>
-  </si>
-  <si>
-    <t>PLB_EQS_WC suspendu_Porcher Matura + Presto:Bâti-support 18460 + cuvette R003001</t>
-  </si>
-  <si>
-    <t>Bâti-support 18460 + cuvette R003001</t>
-  </si>
-  <si>
-    <t>PLB_EQS_Évier granit:970 x 500 x 220 mm + mitigeur</t>
-  </si>
-  <si>
-    <t>970 x 500 x 220 mm + mitigeur</t>
+    <t>Vanne</t>
+  </si>
+  <si>
+    <t>CVC_ACA_Vanne 3 voies:DN15 - Kvs 0,63 - actionneur LR24A-SR-TP</t>
+  </si>
+  <si>
+    <t>DN15 - Kvs 0,63 - actionneur LR24A-SR-TP</t>
+  </si>
+  <si>
+    <t>CVC_ACA_Vanne d'équilibrage_IMI STAD:DN15</t>
+  </si>
+  <si>
+    <t>DN15</t>
+  </si>
+  <si>
+    <t>CVC_ACA_Vanne de pression différentielle_IMI STAP:DN15</t>
+  </si>
+  <si>
+    <t>PLB_ACA_Clapet anti-pollution à brides:DN65</t>
+  </si>
+  <si>
+    <t>DN65</t>
+  </si>
+  <si>
+    <t>PLB_ACA_Clapet anti-pollution:MF - DN15 à DN50</t>
+  </si>
+  <si>
+    <t>MF - DN15 à DN50</t>
+  </si>
+  <si>
+    <t>PLB_ACA_Disconnecteur:DN15</t>
+  </si>
+  <si>
+    <t>PLB_ACA_Disconnecteur_Caleffi 575:DN50</t>
+  </si>
+  <si>
+    <t>PLB_ACA_Robinet de puisage:DN15</t>
+  </si>
+  <si>
+    <t>PLB_ACA_Robinet à boisseau sphérique avec raccord MF:NO</t>
+  </si>
+  <si>
+    <t>PLB_ACA_Réducteur de pression_Caleffi 5366:DN50</t>
+  </si>
+  <si>
+    <t>PLB_ACA_Vanne d’arrêt circulaire:Standard</t>
+  </si>
+  <si>
+    <t>PLB_ACA_Vanne d’arrêt:Standard</t>
+  </si>
+  <si>
+    <t>PLB_ACA_Vanne papillon à brides:DN50</t>
   </si>
   <si>
     <t>PLB_ROB_Robinet de puisage:Standard</t>
   </si>
   <si>
-    <t>Tuyau</t>
+    <t>Élément Flux de Distribution</t>
+  </si>
+  <si>
+    <t>IfcDistributionFlowElement</t>
+  </si>
+  <si>
+    <t>PLB_RBS_ROBINET_BOISSEAU_SPHÉRIQUE:NO</t>
   </si>
   <si>
     <t>Élément de distribution</t>
   </si>
   <si>
-    <t>CVC_ACA_Clapet anti-retour:Standard</t>
+    <t>CVC_ACA_Manomètre:Vertical</t>
   </si>
   <si>
     <t>IfcDistributionControlElement</t>
   </si>
   <si>
-    <t>04_Accessoires de Canalisations</t>
-  </si>
-  <si>
-    <t>CVC_ACA_Disconnecteur_Type EA:Standard</t>
-  </si>
-  <si>
-    <t>CVC_ACA_Filtre à tamis:DN32</t>
-  </si>
-  <si>
-    <t>CVC_ACA_Filtre:Standard</t>
-  </si>
-  <si>
-    <t>CVC_ACA_Manomètre vertical:Vertical</t>
-  </si>
-  <si>
-    <t>CVC_ACA_Purgeur automatique_Flamco:Flexvent G3/8</t>
-  </si>
-  <si>
-    <t>CVC_ACA_Purgeur d'air:DN25</t>
-  </si>
-  <si>
     <t>CVC_ACA_Sonde de température:PT100</t>
   </si>
   <si>
-    <t>CVC_ACA_Soupape de sécurité_Caleffi:DN15-DN32</t>
-  </si>
-  <si>
-    <t>CVC_ACA_Séparateur d'air_IMI Zeparo:ZUV 32</t>
-  </si>
-  <si>
-    <t>CVC_ACA_Séparateur de boues_IMI Zeparo Cyclone:ZCD 30 G1</t>
-  </si>
-  <si>
     <t>CVC_ACA_Thermomètre équerre:H150 mm</t>
   </si>
   <si>
-    <t>CVC_EQH_Adoucisseur_BWT_PRO L 50 MAX:20 m³/h</t>
-  </si>
-  <si>
-    <t>23_Adoucisseurs</t>
-  </si>
-  <si>
-    <t>CVC_EQH_Vase d'expansion:50 L</t>
-  </si>
-  <si>
-    <t>19_Vase à expansion</t>
-  </si>
-  <si>
-    <t>CVC_EQH_Vase d'expansion:8 L</t>
-  </si>
-  <si>
     <t>CVC_TAB_Thermostat_Eurapo:Rond analogique encastré blanc</t>
+  </si>
+  <si>
+    <t>M_Valve_Manometer_MEPcontent_Generic:Vertical</t>
+  </si>
+  <si>
+    <t>PLB_ACA_Manomètre vertical:Vertical</t>
   </si>
 </sst>
 </file>
@@ -1290,6 +1527,16 @@
     </fill>
     <fill>
       <patternFill patternType="none">
+        <fgColor rgb="FFBBBB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBBBB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="none">
         <fgColor rgb="CCFF99"/>
       </patternFill>
     </fill>
@@ -1310,6 +1557,16 @@
     </fill>
     <fill>
       <patternFill patternType="none">
+        <fgColor rgb="333333"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="333333"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="none">
         <fgColor rgb="999999"/>
       </patternFill>
     </fill>
@@ -1386,26 +1643,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="CC99FF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="none">
-        <fgColor rgb="FFBBBB"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBBBB"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="none">
-        <fgColor rgb="333333"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="333333"/>
       </patternFill>
     </fill>
     <fill>
@@ -1530,7 +1767,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:G173"/>
+  <dimension ref="A1:G216"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1564,16 +1801,16 @@
         <v>8</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E2" t="s" s="0">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F2" t="n" s="0">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G2" s="2"/>
     </row>
@@ -1582,19 +1819,19 @@
         <v>7</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D3" t="s" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E3" t="s" s="0">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F3" t="n" s="0">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="G3" s="3"/>
     </row>
@@ -1603,16 +1840,16 @@
         <v>7</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D4" t="s" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E4" t="s" s="0">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F4" t="n" s="0">
         <v>2.0</v>
@@ -1621,40 +1858,40 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D5" t="s" s="0">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="E5" t="s" s="0">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="F5" t="n" s="0">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G5" s="5"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="D6" t="s" s="0">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="E6" t="s" s="0">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F6" t="n" s="0">
         <v>1.0</v>
@@ -1663,19 +1900,19 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="C7" t="s" s="0">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D7" t="s" s="0">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E7" t="s" s="0">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="F7" t="n" s="0">
         <v>1.0</v>
@@ -1684,82 +1921,82 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="C8" t="s" s="0">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="D8" t="s" s="0">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E8" t="s" s="0">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F8" t="n" s="0">
-        <v>11.0</v>
+        <v>1.0</v>
       </c>
       <c r="G8" s="8"/>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C9" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="D9" t="s" s="0">
         <v>28</v>
       </c>
-      <c r="D9" t="s" s="0">
-        <v>25</v>
-      </c>
       <c r="E9" t="s" s="0">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F9" t="n" s="0">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
       <c r="G9" s="9"/>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C10" t="s" s="0">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D10" t="s" s="0">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E10" t="s" s="0">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F10" t="n" s="0">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="G10" s="10"/>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C11" t="s" s="0">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D11" t="s" s="0">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E11" t="s" s="0">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="F11" t="n" s="0">
         <v>1.0</v>
@@ -1768,406 +2005,406 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="C12" t="s" s="0">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="D12" t="s" s="0">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="E12" t="s" s="0">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="F12" t="n" s="0">
-        <v>93.0</v>
-      </c>
-      <c r="G12" s="9"/>
+        <v>1.0</v>
+      </c>
+      <c r="G12" s="12"/>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="C13" t="s" s="0">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="D13" t="s" s="0">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="E13" t="s" s="0">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="F13" t="n" s="0">
-        <v>4.0</v>
-      </c>
-      <c r="G13" s="9"/>
+        <v>1.0</v>
+      </c>
+      <c r="G13" s="13"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="C14" t="s" s="0">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="D14" t="s" s="0">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="E14" t="s" s="0">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="F14" t="n" s="0">
-        <v>1.0</v>
-      </c>
-      <c r="G14" s="12"/>
+        <v>4.0</v>
+      </c>
+      <c r="G14" s="14"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="C15" t="s" s="0">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="D15" t="s" s="0">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="E15" t="s" s="0">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="F15" t="n" s="0">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="G15" s="10"/>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="C16" t="s" s="0">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="D16" t="s" s="0">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="E16" t="s" s="0">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="F16" t="n" s="0">
-        <v>4.0</v>
-      </c>
-      <c r="G16" s="13"/>
+        <v>11.0</v>
+      </c>
+      <c r="G16" s="15"/>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="B17" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="C17" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="D17" t="s" s="0">
         <v>41</v>
       </c>
-      <c r="C17" t="s" s="0">
-        <v>28</v>
-      </c>
-      <c r="D17" t="s" s="0">
+      <c r="E17" t="s" s="0">
         <v>25</v>
       </c>
-      <c r="E17" t="s" s="0">
-        <v>29</v>
-      </c>
       <c r="F17" t="n" s="0">
-        <v>8.0</v>
+        <v>1.0</v>
       </c>
       <c r="G17" s="9"/>
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="C18" t="s" s="0">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="D18" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="E18" t="s" s="0">
         <v>25</v>
       </c>
-      <c r="E18" t="s" s="0">
-        <v>43</v>
-      </c>
       <c r="F18" t="n" s="0">
-        <v>3.0</v>
-      </c>
-      <c r="G18" s="9"/>
+        <v>2.0</v>
+      </c>
+      <c r="G18" s="16"/>
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="B19" t="s" s="0">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="C19" t="s" s="0">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="D19" t="s" s="0">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="E19" t="s" s="0">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="F19" t="n" s="0">
-        <v>59.0</v>
-      </c>
-      <c r="G19" s="9"/>
+        <v>2.0</v>
+      </c>
+      <c r="G19" s="17"/>
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="B20" t="s" s="0">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="C20" t="s" s="0">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D20" t="s" s="0">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="E20" t="s" s="0">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F20" t="n" s="0">
         <v>1.0</v>
       </c>
-      <c r="G20" s="14"/>
+      <c r="G20" s="10"/>
     </row>
     <row r="21">
       <c r="A21" t="s" s="0">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="B21" t="s" s="0">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="C21" t="s" s="0">
-        <v>28</v>
+        <v>59</v>
       </c>
       <c r="D21" t="s" s="0">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="E21" t="s" s="0">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="F21" t="n" s="0">
-        <v>21.0</v>
-      </c>
-      <c r="G21" s="9"/>
+        <v>2.0</v>
+      </c>
+      <c r="G21" s="11"/>
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="B22" t="s" s="0">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="C22" t="s" s="0">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="D22" t="s" s="0">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="E22" t="s" s="0">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="F22" t="n" s="0">
-        <v>33.0</v>
+        <v>12.0</v>
       </c>
       <c r="G22" s="9"/>
     </row>
     <row r="23">
       <c r="A23" t="s" s="0">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="B23" t="s" s="0">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="C23" t="s" s="0">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="D23" t="s" s="0">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="E23" t="s" s="0">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="F23" t="n" s="0">
-        <v>5.0</v>
-      </c>
-      <c r="G23" s="15"/>
+        <v>1.0</v>
+      </c>
+      <c r="G23" s="11"/>
     </row>
     <row r="24">
       <c r="A24" t="s" s="0">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="B24" t="s" s="0">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="C24" t="s" s="0">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="D24" t="s" s="0">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="E24" t="s" s="0">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="F24" t="n" s="0">
-        <v>5.0</v>
-      </c>
-      <c r="G24" s="16"/>
+        <v>4.0</v>
+      </c>
+      <c r="G24" s="18"/>
     </row>
     <row r="25">
       <c r="A25" t="s" s="0">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="B25" t="s" s="0">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="C25" t="s" s="0">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="D25" t="s" s="0">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="E25" t="s" s="0">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="F25" t="n" s="0">
-        <v>5.0</v>
-      </c>
-      <c r="G25" s="17"/>
+        <v>3.0</v>
+      </c>
+      <c r="G25" s="9"/>
     </row>
     <row r="26">
       <c r="A26" t="s" s="0">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="B26" t="s" s="0">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="C26" t="s" s="0">
-        <v>28</v>
+        <v>66</v>
       </c>
       <c r="D26" t="s" s="0">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="E26" t="s" s="0">
-        <v>59</v>
+        <v>32</v>
       </c>
       <c r="F26" t="n" s="0">
-        <v>1.0</v>
-      </c>
-      <c r="G26" s="9"/>
+        <v>3.0</v>
+      </c>
+      <c r="G26" s="19"/>
     </row>
     <row r="27">
       <c r="A27" t="s" s="0">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="B27" t="s" s="0">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="C27" t="s" s="0">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="D27" t="s" s="0">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="E27" t="s" s="0">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="F27" t="n" s="0">
-        <v>1.0</v>
-      </c>
-      <c r="G27" s="18"/>
+        <v>7.0</v>
+      </c>
+      <c r="G27" s="20"/>
     </row>
     <row r="28">
       <c r="A28" t="s" s="0">
-        <v>63</v>
+        <v>38</v>
       </c>
       <c r="B28" t="s" s="0">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="C28" t="s" s="0">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="D28" t="s" s="0">
-        <v>66</v>
+        <v>41</v>
       </c>
       <c r="E28" t="s" s="0">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="F28" t="n" s="0">
-        <v>1.0</v>
-      </c>
-      <c r="G28" s="19"/>
+        <v>3.0</v>
+      </c>
+      <c r="G28" s="21"/>
     </row>
     <row r="29">
       <c r="A29" t="s" s="0">
-        <v>67</v>
+        <v>38</v>
       </c>
       <c r="B29" t="s" s="0">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C29" t="s" s="0">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D29" t="s" s="0">
-        <v>70</v>
+        <v>41</v>
       </c>
       <c r="E29" t="s" s="0">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="F29" t="n" s="0">
-        <v>2.0</v>
-      </c>
-      <c r="G29" s="20"/>
+        <v>59.0</v>
+      </c>
+      <c r="G29" s="21"/>
     </row>
     <row r="30">
       <c r="A30" t="s" s="0">
-        <v>71</v>
+        <v>38</v>
       </c>
       <c r="B30" t="s" s="0">
         <v>72</v>
       </c>
       <c r="C30" t="s" s="0">
-        <v>28</v>
+        <v>73</v>
       </c>
       <c r="D30" t="s" s="0">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="E30" t="s" s="0">
-        <v>59</v>
+        <v>32</v>
       </c>
       <c r="F30" t="n" s="0">
-        <v>6.0</v>
-      </c>
-      <c r="G30" s="9"/>
+        <v>1.0</v>
+      </c>
+      <c r="G30" s="22"/>
     </row>
     <row r="31">
       <c r="A31" t="s" s="0">
-        <v>71</v>
+        <v>38</v>
       </c>
       <c r="B31" t="s" s="0">
         <v>74</v>
@@ -2176,19 +2413,19 @@
         <v>75</v>
       </c>
       <c r="D31" t="s" s="0">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="E31" t="s" s="0">
-        <v>59</v>
+        <v>25</v>
       </c>
       <c r="F31" t="n" s="0">
-        <v>10.0</v>
-      </c>
-      <c r="G31" s="21"/>
+        <v>5.0</v>
+      </c>
+      <c r="G31" s="15"/>
     </row>
     <row r="32">
       <c r="A32" t="s" s="0">
-        <v>71</v>
+        <v>38</v>
       </c>
       <c r="B32" t="s" s="0">
         <v>76</v>
@@ -2197,133 +2434,133 @@
         <v>77</v>
       </c>
       <c r="D32" t="s" s="0">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="E32" t="s" s="0">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="F32" t="n" s="0">
-        <v>16.0</v>
-      </c>
-      <c r="G32" s="22"/>
+        <v>11.0</v>
+      </c>
+      <c r="G32" s="23"/>
     </row>
     <row r="33">
       <c r="A33" t="s" s="0">
-        <v>71</v>
+        <v>38</v>
       </c>
       <c r="B33" t="s" s="0">
         <v>78</v>
       </c>
       <c r="C33" t="s" s="0">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D33" t="s" s="0">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="E33" t="s" s="0">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="F33" t="n" s="0">
-        <v>38.0</v>
-      </c>
-      <c r="G33" s="22"/>
+        <v>29.0</v>
+      </c>
+      <c r="G33" s="24"/>
     </row>
     <row r="34">
       <c r="A34" t="s" s="0">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="B34" t="s" s="0">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C34" t="s" s="0">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D34" t="s" s="0">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="E34" t="s" s="0">
-        <v>81</v>
+        <v>29</v>
       </c>
       <c r="F34" t="n" s="0">
         <v>1.0</v>
       </c>
-      <c r="G34" s="23"/>
+      <c r="G34" s="25"/>
     </row>
     <row r="35">
       <c r="A35" t="s" s="0">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B35" t="s" s="0">
+        <v>84</v>
+      </c>
+      <c r="C35" t="s" s="0">
+        <v>85</v>
+      </c>
+      <c r="D35" t="s" s="0">
         <v>83</v>
-      </c>
-      <c r="C35" t="s" s="0">
-        <v>84</v>
-      </c>
-      <c r="D35" t="s" s="0">
-        <v>85</v>
       </c>
       <c r="E35" t="s" s="0">
         <v>86</v>
       </c>
       <c r="F35" t="n" s="0">
-        <v>22.0</v>
-      </c>
-      <c r="G35" s="24"/>
+        <v>1.0</v>
+      </c>
+      <c r="G35" s="26"/>
     </row>
     <row r="36">
       <c r="A36" t="s" s="0">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="B36" t="s" s="0">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C36" t="s" s="0">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="D36" t="s" s="0">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="E36" t="s" s="0">
-        <v>86</v>
+        <v>29</v>
       </c>
       <c r="F36" t="n" s="0">
-        <v>3.0</v>
-      </c>
-      <c r="G36" s="24"/>
+        <v>1.0</v>
+      </c>
+      <c r="G36" s="19"/>
     </row>
     <row r="37">
       <c r="A37" t="s" s="0">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B37" t="s" s="0">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C37" t="s" s="0">
-        <v>28</v>
+        <v>59</v>
       </c>
       <c r="D37" t="s" s="0">
-        <v>85</v>
+        <v>41</v>
       </c>
       <c r="E37" t="s" s="0">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="F37" t="n" s="0">
-        <v>4.0</v>
-      </c>
-      <c r="G37" s="9"/>
+        <v>1.0</v>
+      </c>
+      <c r="G37" s="11"/>
     </row>
     <row r="38">
       <c r="A38" t="s" s="0">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B38" t="s" s="0">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C38" t="s" s="0">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="D38" t="s" s="0">
-        <v>85</v>
+        <v>41</v>
       </c>
       <c r="E38" t="s" s="0">
         <v>93</v>
@@ -2331,20 +2568,20 @@
       <c r="F38" t="n" s="0">
         <v>1.0</v>
       </c>
-      <c r="G38" s="25"/>
+      <c r="G38" s="27"/>
     </row>
     <row r="39">
       <c r="A39" t="s" s="0">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B39" t="s" s="0">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C39" t="s" s="0">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D39" t="s" s="0">
-        <v>85</v>
+        <v>41</v>
       </c>
       <c r="E39" t="s" s="0">
         <v>93</v>
@@ -2352,41 +2589,41 @@
       <c r="F39" t="n" s="0">
         <v>1.0</v>
       </c>
-      <c r="G39" s="26"/>
+      <c r="G39" s="28"/>
     </row>
     <row r="40">
       <c r="A40" t="s" s="0">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B40" t="s" s="0">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C40" t="s" s="0">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="D40" t="s" s="0">
-        <v>85</v>
+        <v>41</v>
       </c>
       <c r="E40" t="s" s="0">
         <v>93</v>
       </c>
       <c r="F40" t="n" s="0">
-        <v>2.0</v>
-      </c>
-      <c r="G40" s="25"/>
+        <v>5.0</v>
+      </c>
+      <c r="G40" s="29"/>
     </row>
     <row r="41">
       <c r="A41" t="s" s="0">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B41" t="s" s="0">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C41" t="s" s="0">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="D41" t="s" s="0">
-        <v>85</v>
+        <v>41</v>
       </c>
       <c r="E41" t="s" s="0">
         <v>93</v>
@@ -2394,128 +2631,128 @@
       <c r="F41" t="n" s="0">
         <v>1.0</v>
       </c>
-      <c r="G41" s="25"/>
+      <c r="G41" s="30"/>
     </row>
     <row r="42">
       <c r="A42" t="s" s="0">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="B42" t="s" s="0">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="C42" t="s" s="0">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="D42" t="s" s="0">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E42" t="s" s="0">
-        <v>86</v>
+        <v>37</v>
       </c>
       <c r="F42" t="n" s="0">
-        <v>73.0</v>
-      </c>
-      <c r="G42" s="27"/>
+        <v>1.0</v>
+      </c>
+      <c r="G42" s="31"/>
     </row>
     <row r="43">
       <c r="A43" t="s" s="0">
-        <v>88</v>
+        <v>105</v>
       </c>
       <c r="B43" t="s" s="0">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="C43" t="s" s="0">
-        <v>101</v>
+        <v>70</v>
       </c>
       <c r="D43" t="s" s="0">
-        <v>85</v>
+        <v>28</v>
       </c>
       <c r="E43" t="s" s="0">
-        <v>86</v>
+        <v>32</v>
       </c>
       <c r="F43" t="n" s="0">
-        <v>13.0</v>
-      </c>
-      <c r="G43" s="28"/>
+        <v>2.0</v>
+      </c>
+      <c r="G43" s="21"/>
     </row>
     <row r="44">
       <c r="A44" t="s" s="0">
-        <v>88</v>
+        <v>105</v>
       </c>
       <c r="B44" t="s" s="0">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="C44" t="s" s="0">
-        <v>103</v>
+        <v>59</v>
       </c>
       <c r="D44" t="s" s="0">
-        <v>85</v>
+        <v>28</v>
       </c>
       <c r="E44" t="s" s="0">
-        <v>86</v>
+        <v>32</v>
       </c>
       <c r="F44" t="n" s="0">
-        <v>39.0</v>
-      </c>
-      <c r="G44" s="29"/>
+        <v>1.0</v>
+      </c>
+      <c r="G44" s="11"/>
     </row>
     <row r="45">
       <c r="A45" t="s" s="0">
-        <v>88</v>
+        <v>108</v>
       </c>
       <c r="B45" t="s" s="0">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="C45" t="s" s="0">
-        <v>28</v>
+        <v>109</v>
       </c>
       <c r="D45" t="s" s="0">
-        <v>85</v>
+        <v>110</v>
       </c>
       <c r="E45" t="s" s="0">
-        <v>86</v>
+        <v>111</v>
       </c>
       <c r="F45" t="n" s="0">
-        <v>4.0</v>
-      </c>
-      <c r="G45" s="9"/>
+        <v>1.0</v>
+      </c>
+      <c r="G45" s="32"/>
     </row>
     <row r="46">
       <c r="A46" t="s" s="0">
-        <v>88</v>
+        <v>112</v>
       </c>
       <c r="B46" t="s" s="0">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="C46" t="s" s="0">
-        <v>106</v>
+        <v>52</v>
       </c>
       <c r="D46" t="s" s="0">
-        <v>85</v>
+        <v>114</v>
       </c>
       <c r="E46" t="s" s="0">
-        <v>86</v>
+        <v>29</v>
       </c>
       <c r="F46" t="n" s="0">
-        <v>59.0</v>
-      </c>
-      <c r="G46" s="30"/>
+        <v>6.0</v>
+      </c>
+      <c r="G46" s="9"/>
     </row>
     <row r="47">
       <c r="A47" t="s" s="0">
-        <v>88</v>
+        <v>112</v>
       </c>
       <c r="B47" t="s" s="0">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="C47" t="s" s="0">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="D47" t="s" s="0">
-        <v>85</v>
+        <v>114</v>
       </c>
       <c r="E47" t="s" s="0">
-        <v>86</v>
+        <v>29</v>
       </c>
       <c r="F47" t="n" s="0">
         <v>1.0</v>
@@ -2524,1981 +2761,1981 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="0">
-        <v>88</v>
+        <v>112</v>
       </c>
       <c r="B48" t="s" s="0">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="C48" t="s" s="0">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="D48" t="s" s="0">
-        <v>85</v>
+        <v>114</v>
       </c>
       <c r="E48" t="s" s="0">
-        <v>86</v>
+        <v>118</v>
       </c>
       <c r="F48" t="n" s="0">
-        <v>2.0</v>
-      </c>
-      <c r="G48" s="31"/>
+        <v>1.0</v>
+      </c>
+      <c r="G48" s="23"/>
     </row>
     <row r="49">
       <c r="A49" t="s" s="0">
-        <v>88</v>
+        <v>119</v>
       </c>
       <c r="B49" t="s" s="0">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="C49" t="s" s="0">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="D49" t="s" s="0">
-        <v>85</v>
+        <v>122</v>
       </c>
       <c r="E49" t="s" s="0">
-        <v>86</v>
+        <v>29</v>
       </c>
       <c r="F49" t="n" s="0">
-        <v>44.0</v>
-      </c>
-      <c r="G49" s="31"/>
+        <v>10.0</v>
+      </c>
+      <c r="G49" s="21"/>
     </row>
     <row r="50">
       <c r="A50" t="s" s="0">
-        <v>88</v>
+        <v>119</v>
       </c>
       <c r="B50" t="s" s="0">
-        <v>111</v>
+        <v>123</v>
       </c>
       <c r="C50" t="s" s="0">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="D50" t="s" s="0">
-        <v>85</v>
+        <v>122</v>
       </c>
       <c r="E50" t="s" s="0">
-        <v>86</v>
+        <v>29</v>
       </c>
       <c r="F50" t="n" s="0">
-        <v>17.0</v>
-      </c>
-      <c r="G50" s="32"/>
+        <v>16.0</v>
+      </c>
+      <c r="G50" s="22"/>
     </row>
     <row r="51">
       <c r="A51" t="s" s="0">
-        <v>88</v>
+        <v>119</v>
       </c>
       <c r="B51" t="s" s="0">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="C51" t="s" s="0">
-        <v>28</v>
+        <v>124</v>
       </c>
       <c r="D51" t="s" s="0">
-        <v>85</v>
+        <v>122</v>
       </c>
       <c r="E51" t="s" s="0">
-        <v>86</v>
+        <v>29</v>
       </c>
       <c r="F51" t="n" s="0">
-        <v>16.0</v>
-      </c>
-      <c r="G51" s="9"/>
+        <v>38.0</v>
+      </c>
+      <c r="G51" s="22"/>
     </row>
     <row r="52">
       <c r="A52" t="s" s="0">
-        <v>88</v>
+        <v>11</v>
       </c>
       <c r="B52" t="s" s="0">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="C52" t="s" s="0">
-        <v>84</v>
+        <v>126</v>
       </c>
       <c r="D52" t="s" s="0">
-        <v>85</v>
+        <v>10</v>
       </c>
       <c r="E52" t="s" s="0">
-        <v>86</v>
+        <v>11</v>
       </c>
       <c r="F52" t="n" s="0">
-        <v>288.0</v>
-      </c>
-      <c r="G52" s="24"/>
+        <v>2.0</v>
+      </c>
+      <c r="G52" s="33"/>
     </row>
     <row r="53">
       <c r="A53" t="s" s="0">
-        <v>88</v>
+        <v>127</v>
       </c>
       <c r="B53" t="s" s="0">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="C53" t="s" s="0">
-        <v>84</v>
+        <v>52</v>
       </c>
       <c r="D53" t="s" s="0">
-        <v>85</v>
+        <v>129</v>
       </c>
       <c r="E53" t="s" s="0">
-        <v>86</v>
+        <v>130</v>
       </c>
       <c r="F53" t="n" s="0">
-        <v>120.0</v>
-      </c>
-      <c r="G53" s="24"/>
+        <v>15.0</v>
+      </c>
+      <c r="G53" s="9"/>
     </row>
     <row r="54">
       <c r="A54" t="s" s="0">
-        <v>88</v>
+        <v>127</v>
       </c>
       <c r="B54" t="s" s="0">
-        <v>116</v>
+        <v>131</v>
       </c>
       <c r="C54" t="s" s="0">
-        <v>84</v>
+        <v>132</v>
       </c>
       <c r="D54" t="s" s="0">
-        <v>85</v>
+        <v>129</v>
       </c>
       <c r="E54" t="s" s="0">
-        <v>86</v>
+        <v>130</v>
       </c>
       <c r="F54" t="n" s="0">
         <v>17.0</v>
       </c>
-      <c r="G54" s="24"/>
+      <c r="G54" s="30"/>
     </row>
     <row r="55">
       <c r="A55" t="s" s="0">
-        <v>88</v>
+        <v>127</v>
       </c>
       <c r="B55" t="s" s="0">
-        <v>117</v>
+        <v>133</v>
       </c>
       <c r="C55" t="s" s="0">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="D55" t="s" s="0">
-        <v>85</v>
+        <v>129</v>
       </c>
       <c r="E55" t="s" s="0">
-        <v>86</v>
+        <v>130</v>
       </c>
       <c r="F55" t="n" s="0">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G55" s="9"/>
     </row>
     <row r="56">
       <c r="A56" t="s" s="0">
-        <v>88</v>
+        <v>127</v>
       </c>
       <c r="B56" t="s" s="0">
-        <v>118</v>
+        <v>134</v>
       </c>
       <c r="C56" t="s" s="0">
-        <v>28</v>
+        <v>135</v>
       </c>
       <c r="D56" t="s" s="0">
-        <v>85</v>
+        <v>129</v>
       </c>
       <c r="E56" t="s" s="0">
-        <v>86</v>
+        <v>130</v>
       </c>
       <c r="F56" t="n" s="0">
-        <v>19.0</v>
-      </c>
-      <c r="G56" s="9"/>
+        <v>1.0</v>
+      </c>
+      <c r="G56" s="31"/>
     </row>
     <row r="57">
       <c r="A57" t="s" s="0">
-        <v>88</v>
+        <v>127</v>
       </c>
       <c r="B57" t="s" s="0">
-        <v>119</v>
+        <v>136</v>
       </c>
       <c r="C57" t="s" s="0">
-        <v>120</v>
+        <v>137</v>
       </c>
       <c r="D57" t="s" s="0">
-        <v>85</v>
+        <v>129</v>
       </c>
       <c r="E57" t="s" s="0">
-        <v>90</v>
+        <v>130</v>
       </c>
       <c r="F57" t="n" s="0">
-        <v>1.0</v>
-      </c>
-      <c r="G57" s="33"/>
+        <v>5.0</v>
+      </c>
+      <c r="G57" s="32"/>
     </row>
     <row r="58">
       <c r="A58" t="s" s="0">
-        <v>88</v>
+        <v>127</v>
       </c>
       <c r="B58" t="s" s="0">
-        <v>121</v>
+        <v>138</v>
       </c>
       <c r="C58" t="s" s="0">
-        <v>122</v>
+        <v>139</v>
       </c>
       <c r="D58" t="s" s="0">
-        <v>85</v>
+        <v>129</v>
       </c>
       <c r="E58" t="s" s="0">
-        <v>90</v>
+        <v>130</v>
       </c>
       <c r="F58" t="n" s="0">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="G58" s="34"/>
     </row>
     <row r="59">
       <c r="A59" t="s" s="0">
-        <v>88</v>
+        <v>127</v>
       </c>
       <c r="B59" t="s" s="0">
-        <v>123</v>
+        <v>140</v>
       </c>
       <c r="C59" t="s" s="0">
-        <v>124</v>
+        <v>52</v>
       </c>
       <c r="D59" t="s" s="0">
-        <v>85</v>
+        <v>129</v>
       </c>
       <c r="E59" t="s" s="0">
-        <v>90</v>
+        <v>130</v>
       </c>
       <c r="F59" t="n" s="0">
-        <v>3.0</v>
-      </c>
-      <c r="G59" s="35"/>
+        <v>7.0</v>
+      </c>
+      <c r="G59" s="9"/>
     </row>
     <row r="60">
       <c r="A60" t="s" s="0">
-        <v>88</v>
+        <v>127</v>
       </c>
       <c r="B60" t="s" s="0">
-        <v>125</v>
+        <v>141</v>
       </c>
       <c r="C60" t="s" s="0">
-        <v>126</v>
+        <v>142</v>
       </c>
       <c r="D60" t="s" s="0">
-        <v>85</v>
+        <v>129</v>
       </c>
       <c r="E60" t="s" s="0">
-        <v>90</v>
+        <v>130</v>
       </c>
       <c r="F60" t="n" s="0">
-        <v>2.0</v>
-      </c>
-      <c r="G60" s="36"/>
+        <v>31.0</v>
+      </c>
+      <c r="G60" s="35"/>
     </row>
     <row r="61">
       <c r="A61" t="s" s="0">
-        <v>88</v>
+        <v>127</v>
       </c>
       <c r="B61" t="s" s="0">
-        <v>127</v>
+        <v>143</v>
       </c>
       <c r="C61" t="s" s="0">
-        <v>128</v>
+        <v>52</v>
       </c>
       <c r="D61" t="s" s="0">
-        <v>85</v>
+        <v>129</v>
       </c>
       <c r="E61" t="s" s="0">
-        <v>90</v>
+        <v>130</v>
       </c>
       <c r="F61" t="n" s="0">
-        <v>4.0</v>
-      </c>
-      <c r="G61" s="37"/>
+        <v>2.0</v>
+      </c>
+      <c r="G61" s="9"/>
     </row>
     <row r="62">
       <c r="A62" t="s" s="0">
-        <v>88</v>
+        <v>127</v>
       </c>
       <c r="B62" t="s" s="0">
-        <v>129</v>
+        <v>144</v>
       </c>
       <c r="C62" t="s" s="0">
+        <v>145</v>
+      </c>
+      <c r="D62" t="s" s="0">
+        <v>129</v>
+      </c>
+      <c r="E62" t="s" s="0">
         <v>130</v>
       </c>
-      <c r="D62" t="s" s="0">
-        <v>85</v>
-      </c>
-      <c r="E62" t="s" s="0">
-        <v>90</v>
-      </c>
       <c r="F62" t="n" s="0">
-        <v>13.0</v>
-      </c>
-      <c r="G62" s="38"/>
+        <v>1.0</v>
+      </c>
+      <c r="G62" s="36"/>
     </row>
     <row r="63">
       <c r="A63" t="s" s="0">
-        <v>88</v>
+        <v>127</v>
       </c>
       <c r="B63" t="s" s="0">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="C63" t="s" s="0">
-        <v>132</v>
+        <v>147</v>
       </c>
       <c r="D63" t="s" s="0">
-        <v>85</v>
+        <v>129</v>
       </c>
       <c r="E63" t="s" s="0">
-        <v>90</v>
+        <v>130</v>
       </c>
       <c r="F63" t="n" s="0">
-        <v>6.0</v>
-      </c>
-      <c r="G63" s="39"/>
+        <v>37.0</v>
+      </c>
+      <c r="G63" s="24"/>
     </row>
     <row r="64">
       <c r="A64" t="s" s="0">
-        <v>88</v>
+        <v>127</v>
       </c>
       <c r="B64" t="s" s="0">
-        <v>133</v>
+        <v>148</v>
       </c>
       <c r="C64" t="s" s="0">
-        <v>134</v>
+        <v>52</v>
       </c>
       <c r="D64" t="s" s="0">
-        <v>85</v>
+        <v>129</v>
       </c>
       <c r="E64" t="s" s="0">
-        <v>90</v>
+        <v>130</v>
       </c>
       <c r="F64" t="n" s="0">
-        <v>5.0</v>
-      </c>
-      <c r="G64" s="40"/>
+        <v>11.0</v>
+      </c>
+      <c r="G64" s="9"/>
     </row>
     <row r="65">
       <c r="A65" t="s" s="0">
-        <v>88</v>
+        <v>127</v>
       </c>
       <c r="B65" t="s" s="0">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="C65" t="s" s="0">
-        <v>134</v>
+        <v>52</v>
       </c>
       <c r="D65" t="s" s="0">
-        <v>85</v>
+        <v>129</v>
       </c>
       <c r="E65" t="s" s="0">
-        <v>90</v>
+        <v>130</v>
       </c>
       <c r="F65" t="n" s="0">
-        <v>3.0</v>
-      </c>
-      <c r="G65" s="40"/>
+        <v>2.0</v>
+      </c>
+      <c r="G65" s="9"/>
     </row>
     <row r="66">
       <c r="A66" t="s" s="0">
-        <v>88</v>
+        <v>127</v>
       </c>
       <c r="B66" t="s" s="0">
-        <v>136</v>
+        <v>150</v>
       </c>
       <c r="C66" t="s" s="0">
-        <v>137</v>
+        <v>52</v>
       </c>
       <c r="D66" t="s" s="0">
-        <v>85</v>
+        <v>129</v>
       </c>
       <c r="E66" t="s" s="0">
-        <v>90</v>
+        <v>130</v>
       </c>
       <c r="F66" t="n" s="0">
-        <v>1.0</v>
-      </c>
-      <c r="G66" s="41"/>
+        <v>47.0</v>
+      </c>
+      <c r="G66" s="9"/>
     </row>
     <row r="67">
       <c r="A67" t="s" s="0">
-        <v>88</v>
+        <v>127</v>
       </c>
       <c r="B67" t="s" s="0">
-        <v>138</v>
+        <v>151</v>
       </c>
       <c r="C67" t="s" s="0">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="D67" t="s" s="0">
-        <v>85</v>
+        <v>129</v>
       </c>
       <c r="E67" t="s" s="0">
-        <v>90</v>
+        <v>130</v>
       </c>
       <c r="F67" t="n" s="0">
-        <v>2.0</v>
-      </c>
-      <c r="G67" s="42"/>
+        <v>6.0</v>
+      </c>
+      <c r="G67" s="36"/>
     </row>
     <row r="68">
       <c r="A68" t="s" s="0">
-        <v>88</v>
+        <v>127</v>
       </c>
       <c r="B68" t="s" s="0">
-        <v>140</v>
+        <v>152</v>
       </c>
       <c r="C68" t="s" s="0">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="D68" t="s" s="0">
-        <v>85</v>
+        <v>129</v>
       </c>
       <c r="E68" t="s" s="0">
-        <v>90</v>
+        <v>130</v>
       </c>
       <c r="F68" t="n" s="0">
-        <v>2.0</v>
-      </c>
-      <c r="G68" s="43"/>
+        <v>344.0</v>
+      </c>
+      <c r="G68" s="24"/>
     </row>
     <row r="69">
       <c r="A69" t="s" s="0">
-        <v>88</v>
+        <v>127</v>
       </c>
       <c r="B69" t="s" s="0">
-        <v>142</v>
+        <v>153</v>
       </c>
       <c r="C69" t="s" s="0">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="D69" t="s" s="0">
-        <v>85</v>
+        <v>129</v>
       </c>
       <c r="E69" t="s" s="0">
-        <v>90</v>
+        <v>130</v>
       </c>
       <c r="F69" t="n" s="0">
-        <v>2.0</v>
-      </c>
-      <c r="G69" s="44"/>
+        <v>37.0</v>
+      </c>
+      <c r="G69" s="27"/>
     </row>
     <row r="70">
       <c r="A70" t="s" s="0">
-        <v>88</v>
+        <v>127</v>
       </c>
       <c r="B70" t="s" s="0">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="C70" t="s" s="0">
-        <v>126</v>
+        <v>156</v>
       </c>
       <c r="D70" t="s" s="0">
-        <v>85</v>
+        <v>129</v>
       </c>
       <c r="E70" t="s" s="0">
-        <v>90</v>
+        <v>130</v>
       </c>
       <c r="F70" t="n" s="0">
-        <v>1.0</v>
-      </c>
-      <c r="G70" s="36"/>
+        <v>2.0</v>
+      </c>
+      <c r="G70" s="37"/>
     </row>
     <row r="71">
       <c r="A71" t="s" s="0">
-        <v>88</v>
+        <v>127</v>
       </c>
       <c r="B71" t="s" s="0">
-        <v>145</v>
+        <v>157</v>
       </c>
       <c r="C71" t="s" s="0">
-        <v>126</v>
+        <v>142</v>
       </c>
       <c r="D71" t="s" s="0">
-        <v>85</v>
+        <v>129</v>
       </c>
       <c r="E71" t="s" s="0">
-        <v>90</v>
+        <v>130</v>
       </c>
       <c r="F71" t="n" s="0">
-        <v>3.0</v>
-      </c>
-      <c r="G71" s="36"/>
+        <v>1.0</v>
+      </c>
+      <c r="G71" s="35"/>
     </row>
     <row r="72">
       <c r="A72" t="s" s="0">
-        <v>88</v>
+        <v>127</v>
       </c>
       <c r="B72" t="s" s="0">
-        <v>146</v>
+        <v>158</v>
       </c>
       <c r="C72" t="s" s="0">
-        <v>126</v>
+        <v>142</v>
       </c>
       <c r="D72" t="s" s="0">
-        <v>85</v>
+        <v>129</v>
       </c>
       <c r="E72" t="s" s="0">
-        <v>90</v>
+        <v>130</v>
       </c>
       <c r="F72" t="n" s="0">
-        <v>2.0</v>
-      </c>
-      <c r="G72" s="36"/>
+        <v>15.0</v>
+      </c>
+      <c r="G72" s="35"/>
     </row>
     <row r="73">
       <c r="A73" t="s" s="0">
-        <v>88</v>
+        <v>127</v>
       </c>
       <c r="B73" t="s" s="0">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="C73" t="s" s="0">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="D73" t="s" s="0">
-        <v>85</v>
+        <v>129</v>
       </c>
       <c r="E73" t="s" s="0">
-        <v>90</v>
+        <v>130</v>
       </c>
       <c r="F73" t="n" s="0">
-        <v>7.0</v>
+        <v>2.0</v>
       </c>
       <c r="G73" s="9"/>
     </row>
     <row r="74">
       <c r="A74" t="s" s="0">
-        <v>88</v>
+        <v>127</v>
       </c>
       <c r="B74" t="s" s="0">
-        <v>148</v>
+        <v>160</v>
       </c>
       <c r="C74" t="s" s="0">
-        <v>92</v>
+        <v>52</v>
       </c>
       <c r="D74" t="s" s="0">
-        <v>85</v>
+        <v>129</v>
       </c>
       <c r="E74" t="s" s="0">
-        <v>90</v>
+        <v>130</v>
       </c>
       <c r="F74" t="n" s="0">
-        <v>9.0</v>
-      </c>
-      <c r="G74" s="25"/>
+        <v>4.0</v>
+      </c>
+      <c r="G74" s="9"/>
     </row>
     <row r="75">
       <c r="A75" t="s" s="0">
-        <v>88</v>
+        <v>127</v>
       </c>
       <c r="B75" t="s" s="0">
-        <v>149</v>
+        <v>161</v>
       </c>
       <c r="C75" t="s" s="0">
-        <v>28</v>
+        <v>147</v>
       </c>
       <c r="D75" t="s" s="0">
-        <v>85</v>
+        <v>129</v>
       </c>
       <c r="E75" t="s" s="0">
-        <v>90</v>
+        <v>130</v>
       </c>
       <c r="F75" t="n" s="0">
-        <v>2.0</v>
-      </c>
-      <c r="G75" s="9"/>
+        <v>78.0</v>
+      </c>
+      <c r="G75" s="24"/>
     </row>
     <row r="76">
       <c r="A76" t="s" s="0">
-        <v>88</v>
+        <v>127</v>
       </c>
       <c r="B76" t="s" s="0">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="C76" t="s" s="0">
-        <v>139</v>
+        <v>163</v>
       </c>
       <c r="D76" t="s" s="0">
-        <v>85</v>
+        <v>129</v>
       </c>
       <c r="E76" t="s" s="0">
-        <v>90</v>
+        <v>130</v>
       </c>
       <c r="F76" t="n" s="0">
-        <v>2.0</v>
-      </c>
-      <c r="G76" s="42"/>
+        <v>1.0</v>
+      </c>
+      <c r="G76" s="28"/>
     </row>
     <row r="77">
       <c r="A77" t="s" s="0">
-        <v>88</v>
+        <v>127</v>
       </c>
       <c r="B77" t="s" s="0">
-        <v>151</v>
+        <v>164</v>
       </c>
       <c r="C77" t="s" s="0">
-        <v>141</v>
+        <v>165</v>
       </c>
       <c r="D77" t="s" s="0">
-        <v>85</v>
+        <v>129</v>
       </c>
       <c r="E77" t="s" s="0">
-        <v>90</v>
+        <v>130</v>
       </c>
       <c r="F77" t="n" s="0">
-        <v>2.0</v>
-      </c>
-      <c r="G77" s="43"/>
+        <v>16.0</v>
+      </c>
+      <c r="G77" s="38"/>
     </row>
     <row r="78">
       <c r="A78" t="s" s="0">
-        <v>88</v>
+        <v>127</v>
       </c>
       <c r="B78" t="s" s="0">
-        <v>152</v>
+        <v>166</v>
       </c>
       <c r="C78" t="s" s="0">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D78" t="s" s="0">
-        <v>85</v>
+        <v>129</v>
       </c>
       <c r="E78" t="s" s="0">
-        <v>90</v>
+        <v>130</v>
       </c>
       <c r="F78" t="n" s="0">
-        <v>2.0</v>
-      </c>
-      <c r="G78" s="44"/>
+        <v>101.0</v>
+      </c>
+      <c r="G78" s="35"/>
     </row>
     <row r="79">
       <c r="A79" t="s" s="0">
-        <v>88</v>
+        <v>127</v>
       </c>
       <c r="B79" t="s" s="0">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="C79" t="s" s="0">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="D79" t="s" s="0">
-        <v>85</v>
+        <v>129</v>
       </c>
       <c r="E79" t="s" s="0">
-        <v>90</v>
+        <v>130</v>
       </c>
       <c r="F79" t="n" s="0">
-        <v>2.0</v>
+        <v>9.0</v>
       </c>
       <c r="G79" s="9"/>
     </row>
     <row r="80">
       <c r="A80" t="s" s="0">
-        <v>88</v>
+        <v>127</v>
       </c>
       <c r="B80" t="s" s="0">
-        <v>154</v>
+        <v>168</v>
       </c>
       <c r="C80" t="s" s="0">
-        <v>28</v>
+        <v>145</v>
       </c>
       <c r="D80" t="s" s="0">
-        <v>85</v>
+        <v>129</v>
       </c>
       <c r="E80" t="s" s="0">
-        <v>90</v>
+        <v>130</v>
       </c>
       <c r="F80" t="n" s="0">
-        <v>2.0</v>
-      </c>
-      <c r="G80" s="9"/>
+        <v>1.0</v>
+      </c>
+      <c r="G80" s="36"/>
     </row>
     <row r="81">
       <c r="A81" t="s" s="0">
-        <v>88</v>
+        <v>127</v>
       </c>
       <c r="B81" t="s" s="0">
-        <v>155</v>
+        <v>169</v>
       </c>
       <c r="C81" t="s" s="0">
-        <v>28</v>
+        <v>147</v>
       </c>
       <c r="D81" t="s" s="0">
-        <v>85</v>
+        <v>129</v>
       </c>
       <c r="E81" t="s" s="0">
-        <v>90</v>
+        <v>130</v>
       </c>
       <c r="F81" t="n" s="0">
-        <v>2.0</v>
-      </c>
-      <c r="G81" s="9"/>
+        <v>97.0</v>
+      </c>
+      <c r="G81" s="24"/>
     </row>
     <row r="82">
       <c r="A82" t="s" s="0">
-        <v>88</v>
+        <v>127</v>
       </c>
       <c r="B82" t="s" s="0">
-        <v>156</v>
+        <v>170</v>
       </c>
       <c r="C82" t="s" s="0">
-        <v>157</v>
+        <v>171</v>
       </c>
       <c r="D82" t="s" s="0">
-        <v>85</v>
+        <v>129</v>
       </c>
       <c r="E82" t="s" s="0">
-        <v>86</v>
+        <v>130</v>
       </c>
       <c r="F82" t="n" s="0">
-        <v>32.0</v>
-      </c>
-      <c r="G82" s="45"/>
+        <v>18.0</v>
+      </c>
+      <c r="G82" s="29"/>
     </row>
     <row r="83">
       <c r="A83" t="s" s="0">
-        <v>88</v>
+        <v>127</v>
       </c>
       <c r="B83" t="s" s="0">
-        <v>158</v>
+        <v>172</v>
       </c>
       <c r="C83" t="s" s="0">
-        <v>84</v>
+        <v>147</v>
       </c>
       <c r="D83" t="s" s="0">
-        <v>85</v>
+        <v>129</v>
       </c>
       <c r="E83" t="s" s="0">
-        <v>86</v>
+        <v>130</v>
       </c>
       <c r="F83" t="n" s="0">
-        <v>11.0</v>
+        <v>1.0</v>
       </c>
       <c r="G83" s="24"/>
     </row>
     <row r="84">
       <c r="A84" t="s" s="0">
-        <v>88</v>
+        <v>127</v>
       </c>
       <c r="B84" t="s" s="0">
-        <v>159</v>
+        <v>173</v>
       </c>
       <c r="C84" t="s" s="0">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="D84" t="s" s="0">
-        <v>85</v>
+        <v>129</v>
       </c>
       <c r="E84" t="s" s="0">
-        <v>86</v>
+        <v>130</v>
       </c>
       <c r="F84" t="n" s="0">
-        <v>13.0</v>
+        <v>2.0</v>
       </c>
       <c r="G84" s="9"/>
     </row>
     <row r="85">
       <c r="A85" t="s" s="0">
-        <v>88</v>
+        <v>127</v>
       </c>
       <c r="B85" t="s" s="0">
-        <v>160</v>
+        <v>174</v>
       </c>
       <c r="C85" t="s" s="0">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="D85" t="s" s="0">
-        <v>85</v>
+        <v>129</v>
       </c>
       <c r="E85" t="s" s="0">
-        <v>86</v>
+        <v>130</v>
       </c>
       <c r="F85" t="n" s="0">
-        <v>2.0</v>
+        <v>7.0</v>
       </c>
       <c r="G85" s="9"/>
     </row>
     <row r="86">
       <c r="A86" t="s" s="0">
-        <v>88</v>
+        <v>175</v>
       </c>
       <c r="B86" t="s" s="0">
-        <v>161</v>
+        <v>176</v>
       </c>
       <c r="C86" t="s" s="0">
-        <v>28</v>
+        <v>177</v>
       </c>
       <c r="D86" t="s" s="0">
-        <v>85</v>
+        <v>129</v>
       </c>
       <c r="E86" t="s" s="0">
-        <v>86</v>
+        <v>25</v>
       </c>
       <c r="F86" t="n" s="0">
-        <v>47.0</v>
-      </c>
-      <c r="G86" s="9"/>
+        <v>3.0</v>
+      </c>
+      <c r="G86" s="39"/>
     </row>
     <row r="87">
       <c r="A87" t="s" s="0">
-        <v>88</v>
+        <v>175</v>
       </c>
       <c r="B87" t="s" s="0">
-        <v>83</v>
+        <v>178</v>
       </c>
       <c r="C87" t="s" s="0">
-        <v>84</v>
+        <v>52</v>
       </c>
       <c r="D87" t="s" s="0">
-        <v>85</v>
+        <v>129</v>
       </c>
       <c r="E87" t="s" s="0">
-        <v>86</v>
+        <v>179</v>
       </c>
       <c r="F87" t="n" s="0">
-        <v>300.0</v>
-      </c>
-      <c r="G87" s="24"/>
+        <v>4.0</v>
+      </c>
+      <c r="G87" s="9"/>
     </row>
     <row r="88">
       <c r="A88" t="s" s="0">
-        <v>88</v>
+        <v>175</v>
       </c>
       <c r="B88" t="s" s="0">
-        <v>162</v>
+        <v>180</v>
       </c>
       <c r="C88" t="s" s="0">
-        <v>157</v>
+        <v>181</v>
       </c>
       <c r="D88" t="s" s="0">
-        <v>85</v>
+        <v>129</v>
       </c>
       <c r="E88" t="s" s="0">
-        <v>86</v>
+        <v>182</v>
       </c>
       <c r="F88" t="n" s="0">
         <v>1.0</v>
       </c>
-      <c r="G88" s="45"/>
+      <c r="G88" s="25"/>
     </row>
     <row r="89">
       <c r="A89" t="s" s="0">
-        <v>88</v>
+        <v>175</v>
       </c>
       <c r="B89" t="s" s="0">
-        <v>163</v>
+        <v>183</v>
       </c>
       <c r="C89" t="s" s="0">
-        <v>28</v>
+        <v>184</v>
       </c>
       <c r="D89" t="s" s="0">
-        <v>85</v>
+        <v>129</v>
       </c>
       <c r="E89" t="s" s="0">
-        <v>86</v>
+        <v>182</v>
       </c>
       <c r="F89" t="n" s="0">
-        <v>3.0</v>
-      </c>
-      <c r="G89" s="9"/>
+        <v>1.0</v>
+      </c>
+      <c r="G89" s="26"/>
     </row>
     <row r="90">
       <c r="A90" t="s" s="0">
-        <v>88</v>
+        <v>175</v>
       </c>
       <c r="B90" t="s" s="0">
-        <v>164</v>
+        <v>185</v>
       </c>
       <c r="C90" t="s" s="0">
-        <v>84</v>
+        <v>181</v>
       </c>
       <c r="D90" t="s" s="0">
-        <v>85</v>
+        <v>129</v>
       </c>
       <c r="E90" t="s" s="0">
-        <v>86</v>
+        <v>182</v>
       </c>
       <c r="F90" t="n" s="0">
-        <v>47.0</v>
-      </c>
-      <c r="G90" s="24"/>
+        <v>2.0</v>
+      </c>
+      <c r="G90" s="25"/>
     </row>
     <row r="91">
       <c r="A91" t="s" s="0">
-        <v>88</v>
+        <v>175</v>
       </c>
       <c r="B91" t="s" s="0">
-        <v>165</v>
+        <v>186</v>
       </c>
       <c r="C91" t="s" s="0">
-        <v>166</v>
+        <v>181</v>
       </c>
       <c r="D91" t="s" s="0">
-        <v>85</v>
+        <v>129</v>
       </c>
       <c r="E91" t="s" s="0">
-        <v>86</v>
+        <v>182</v>
       </c>
       <c r="F91" t="n" s="0">
-        <v>12.0</v>
-      </c>
-      <c r="G91" s="46"/>
+        <v>1.0</v>
+      </c>
+      <c r="G91" s="25"/>
     </row>
     <row r="92">
       <c r="A92" t="s" s="0">
-        <v>88</v>
+        <v>175</v>
       </c>
       <c r="B92" t="s" s="0">
-        <v>167</v>
+        <v>128</v>
       </c>
       <c r="C92" t="s" s="0">
-        <v>157</v>
+        <v>52</v>
       </c>
       <c r="D92" t="s" s="0">
-        <v>85</v>
+        <v>129</v>
       </c>
       <c r="E92" t="s" s="0">
-        <v>86</v>
+        <v>130</v>
       </c>
       <c r="F92" t="n" s="0">
         <v>2.0</v>
       </c>
-      <c r="G92" s="45"/>
+      <c r="G92" s="9"/>
     </row>
     <row r="93">
       <c r="A93" t="s" s="0">
-        <v>88</v>
+        <v>175</v>
       </c>
       <c r="B93" t="s" s="0">
-        <v>168</v>
+        <v>131</v>
       </c>
       <c r="C93" t="s" s="0">
-        <v>28</v>
+        <v>132</v>
       </c>
       <c r="D93" t="s" s="0">
-        <v>85</v>
+        <v>129</v>
       </c>
       <c r="E93" t="s" s="0">
-        <v>86</v>
+        <v>130</v>
       </c>
       <c r="F93" t="n" s="0">
-        <v>10.0</v>
-      </c>
-      <c r="G93" s="9"/>
+        <v>46.0</v>
+      </c>
+      <c r="G93" s="30"/>
     </row>
     <row r="94">
       <c r="A94" t="s" s="0">
-        <v>88</v>
+        <v>175</v>
       </c>
       <c r="B94" t="s" s="0">
-        <v>87</v>
+        <v>134</v>
       </c>
       <c r="C94" t="s" s="0">
-        <v>84</v>
+        <v>135</v>
       </c>
       <c r="D94" t="s" s="0">
-        <v>85</v>
+        <v>129</v>
       </c>
       <c r="E94" t="s" s="0">
-        <v>86</v>
+        <v>130</v>
       </c>
       <c r="F94" t="n" s="0">
-        <v>82.0</v>
-      </c>
-      <c r="G94" s="24"/>
+        <v>55.0</v>
+      </c>
+      <c r="G94" s="31"/>
     </row>
     <row r="95">
       <c r="A95" t="s" s="0">
-        <v>88</v>
+        <v>175</v>
       </c>
       <c r="B95" t="s" s="0">
-        <v>169</v>
+        <v>136</v>
       </c>
       <c r="C95" t="s" s="0">
-        <v>84</v>
+        <v>137</v>
       </c>
       <c r="D95" t="s" s="0">
-        <v>85</v>
+        <v>129</v>
       </c>
       <c r="E95" t="s" s="0">
-        <v>86</v>
+        <v>130</v>
       </c>
       <c r="F95" t="n" s="0">
-        <v>1.0</v>
-      </c>
-      <c r="G95" s="24"/>
+        <v>6.0</v>
+      </c>
+      <c r="G95" s="32"/>
     </row>
     <row r="96">
       <c r="A96" t="s" s="0">
-        <v>88</v>
+        <v>175</v>
       </c>
       <c r="B96" t="s" s="0">
-        <v>170</v>
+        <v>140</v>
       </c>
       <c r="C96" t="s" s="0">
-        <v>124</v>
+        <v>52</v>
       </c>
       <c r="D96" t="s" s="0">
-        <v>85</v>
+        <v>129</v>
       </c>
       <c r="E96" t="s" s="0">
-        <v>90</v>
+        <v>130</v>
       </c>
       <c r="F96" t="n" s="0">
-        <v>34.0</v>
-      </c>
-      <c r="G96" s="35"/>
+        <v>29.0</v>
+      </c>
+      <c r="G96" s="9"/>
     </row>
     <row r="97">
       <c r="A97" t="s" s="0">
-        <v>88</v>
+        <v>175</v>
       </c>
       <c r="B97" t="s" s="0">
-        <v>171</v>
+        <v>187</v>
       </c>
       <c r="C97" t="s" s="0">
-        <v>134</v>
+        <v>52</v>
       </c>
       <c r="D97" t="s" s="0">
-        <v>85</v>
+        <v>129</v>
       </c>
       <c r="E97" t="s" s="0">
-        <v>90</v>
+        <v>130</v>
       </c>
       <c r="F97" t="n" s="0">
-        <v>35.0</v>
-      </c>
-      <c r="G97" s="40"/>
+        <v>1.0</v>
+      </c>
+      <c r="G97" s="9"/>
     </row>
     <row r="98">
       <c r="A98" t="s" s="0">
-        <v>88</v>
+        <v>175</v>
       </c>
       <c r="B98" t="s" s="0">
-        <v>172</v>
+        <v>188</v>
       </c>
       <c r="C98" t="s" s="0">
-        <v>28</v>
+        <v>137</v>
       </c>
       <c r="D98" t="s" s="0">
-        <v>85</v>
+        <v>129</v>
       </c>
       <c r="E98" t="s" s="0">
-        <v>90</v>
+        <v>130</v>
       </c>
       <c r="F98" t="n" s="0">
         <v>2.0</v>
       </c>
-      <c r="G98" s="9"/>
+      <c r="G98" s="32"/>
     </row>
     <row r="99">
       <c r="A99" t="s" s="0">
-        <v>88</v>
+        <v>175</v>
       </c>
       <c r="B99" t="s" s="0">
-        <v>173</v>
+        <v>189</v>
       </c>
       <c r="C99" t="s" s="0">
-        <v>28</v>
+        <v>145</v>
       </c>
       <c r="D99" t="s" s="0">
-        <v>85</v>
+        <v>129</v>
       </c>
       <c r="E99" t="s" s="0">
-        <v>93</v>
+        <v>130</v>
       </c>
       <c r="F99" t="n" s="0">
-        <v>2.0</v>
-      </c>
-      <c r="G99" s="9"/>
+        <v>296.0</v>
+      </c>
+      <c r="G99" s="36"/>
     </row>
     <row r="100">
       <c r="A100" t="s" s="0">
-        <v>88</v>
+        <v>175</v>
       </c>
       <c r="B100" t="s" s="0">
-        <v>174</v>
+        <v>190</v>
       </c>
       <c r="C100" t="s" s="0">
-        <v>28</v>
+        <v>145</v>
       </c>
       <c r="D100" t="s" s="0">
-        <v>85</v>
+        <v>129</v>
       </c>
       <c r="E100" t="s" s="0">
-        <v>86</v>
+        <v>130</v>
       </c>
       <c r="F100" t="n" s="0">
-        <v>7.0</v>
-      </c>
-      <c r="G100" s="9"/>
+        <v>43.0</v>
+      </c>
+      <c r="G100" s="36"/>
     </row>
     <row r="101">
       <c r="A101" t="s" s="0">
-        <v>88</v>
+        <v>175</v>
       </c>
       <c r="B101" t="s" s="0">
-        <v>175</v>
+        <v>191</v>
       </c>
       <c r="C101" t="s" s="0">
-        <v>28</v>
+        <v>145</v>
       </c>
       <c r="D101" t="s" s="0">
-        <v>85</v>
+        <v>129</v>
       </c>
       <c r="E101" t="s" s="0">
-        <v>90</v>
+        <v>130</v>
       </c>
       <c r="F101" t="n" s="0">
-        <v>4.0</v>
-      </c>
-      <c r="G101" s="9"/>
+        <v>18.0</v>
+      </c>
+      <c r="G101" s="36"/>
     </row>
     <row r="102">
       <c r="A102" t="s" s="0">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B102" t="s" s="0">
-        <v>177</v>
+        <v>192</v>
       </c>
       <c r="C102" t="s" s="0">
-        <v>178</v>
+        <v>52</v>
       </c>
       <c r="D102" t="s" s="0">
-        <v>179</v>
+        <v>129</v>
       </c>
       <c r="E102" t="s" s="0">
-        <v>180</v>
+        <v>130</v>
       </c>
       <c r="F102" t="n" s="0">
-        <v>23.0</v>
-      </c>
-      <c r="G102" s="47"/>
+        <v>19.0</v>
+      </c>
+      <c r="G102" s="9"/>
     </row>
     <row r="103">
       <c r="A103" t="s" s="0">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B103" t="s" s="0">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="C103" t="s" s="0">
-        <v>182</v>
+        <v>194</v>
       </c>
       <c r="D103" t="s" s="0">
+        <v>129</v>
+      </c>
+      <c r="E103" t="s" s="0">
         <v>179</v>
       </c>
-      <c r="E103" t="s" s="0">
-        <v>180</v>
-      </c>
       <c r="F103" t="n" s="0">
-        <v>363.0</v>
-      </c>
-      <c r="G103" s="48"/>
+        <v>1.0</v>
+      </c>
+      <c r="G103" s="33"/>
     </row>
     <row r="104">
       <c r="A104" t="s" s="0">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B104" t="s" s="0">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="C104" t="s" s="0">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="D104" t="s" s="0">
+        <v>129</v>
+      </c>
+      <c r="E104" t="s" s="0">
         <v>179</v>
       </c>
-      <c r="E104" t="s" s="0">
-        <v>180</v>
-      </c>
       <c r="F104" t="n" s="0">
-        <v>379.0</v>
-      </c>
-      <c r="G104" s="49"/>
+        <v>5.0</v>
+      </c>
+      <c r="G104" s="34"/>
     </row>
     <row r="105">
       <c r="A105" t="s" s="0">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B105" t="s" s="0">
-        <v>185</v>
+        <v>197</v>
       </c>
       <c r="C105" t="s" s="0">
-        <v>186</v>
+        <v>198</v>
       </c>
       <c r="D105" t="s" s="0">
+        <v>129</v>
+      </c>
+      <c r="E105" t="s" s="0">
         <v>179</v>
       </c>
-      <c r="E105" t="s" s="0">
-        <v>180</v>
-      </c>
       <c r="F105" t="n" s="0">
-        <v>77.0</v>
-      </c>
-      <c r="G105" s="50"/>
+        <v>3.0</v>
+      </c>
+      <c r="G105" s="36"/>
     </row>
     <row r="106">
       <c r="A106" t="s" s="0">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B106" t="s" s="0">
-        <v>187</v>
+        <v>199</v>
       </c>
       <c r="C106" t="s" s="0">
-        <v>188</v>
+        <v>200</v>
       </c>
       <c r="D106" t="s" s="0">
+        <v>129</v>
+      </c>
+      <c r="E106" t="s" s="0">
         <v>179</v>
       </c>
-      <c r="E106" t="s" s="0">
-        <v>180</v>
-      </c>
       <c r="F106" t="n" s="0">
-        <v>557.0</v>
-      </c>
-      <c r="G106" s="51"/>
+        <v>2.0</v>
+      </c>
+      <c r="G106" s="37"/>
     </row>
     <row r="107">
       <c r="A107" t="s" s="0">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B107" t="s" s="0">
-        <v>189</v>
+        <v>201</v>
       </c>
       <c r="C107" t="s" s="0">
-        <v>190</v>
+        <v>202</v>
       </c>
       <c r="D107" t="s" s="0">
+        <v>129</v>
+      </c>
+      <c r="E107" t="s" s="0">
         <v>179</v>
       </c>
-      <c r="E107" t="s" s="0">
-        <v>180</v>
-      </c>
       <c r="F107" t="n" s="0">
-        <v>119.0</v>
-      </c>
-      <c r="G107" s="2"/>
+        <v>4.0</v>
+      </c>
+      <c r="G107" s="39"/>
     </row>
     <row r="108">
       <c r="A108" t="s" s="0">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B108" t="s" s="0">
-        <v>191</v>
+        <v>203</v>
       </c>
       <c r="C108" t="s" s="0">
-        <v>192</v>
+        <v>204</v>
       </c>
       <c r="D108" t="s" s="0">
+        <v>129</v>
+      </c>
+      <c r="E108" t="s" s="0">
         <v>179</v>
       </c>
-      <c r="E108" t="s" s="0">
-        <v>180</v>
-      </c>
       <c r="F108" t="n" s="0">
-        <v>317.0</v>
-      </c>
-      <c r="G108" s="3"/>
+        <v>15.0</v>
+      </c>
+      <c r="G108" s="40"/>
     </row>
     <row r="109">
       <c r="A109" t="s" s="0">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B109" t="s" s="0">
-        <v>193</v>
+        <v>205</v>
       </c>
       <c r="C109" t="s" s="0">
-        <v>194</v>
+        <v>206</v>
       </c>
       <c r="D109" t="s" s="0">
+        <v>129</v>
+      </c>
+      <c r="E109" t="s" s="0">
         <v>179</v>
-      </c>
-      <c r="E109" t="s" s="0">
-        <v>180</v>
       </c>
       <c r="F109" t="n" s="0">
         <v>6.0</v>
       </c>
-      <c r="G109" s="4"/>
+      <c r="G109" s="41"/>
     </row>
     <row r="110">
       <c r="A110" t="s" s="0">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B110" t="s" s="0">
-        <v>195</v>
+        <v>207</v>
       </c>
       <c r="C110" t="s" s="0">
-        <v>196</v>
+        <v>208</v>
       </c>
       <c r="D110" t="s" s="0">
+        <v>129</v>
+      </c>
+      <c r="E110" t="s" s="0">
         <v>179</v>
       </c>
-      <c r="E110" t="s" s="0">
-        <v>180</v>
-      </c>
       <c r="F110" t="n" s="0">
-        <v>97.0</v>
-      </c>
-      <c r="G110" s="5"/>
+        <v>5.0</v>
+      </c>
+      <c r="G110" s="42"/>
     </row>
     <row r="111">
       <c r="A111" t="s" s="0">
-        <v>197</v>
+        <v>175</v>
       </c>
       <c r="B111" t="s" s="0">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="C111" t="s" s="0">
-        <v>28</v>
+        <v>208</v>
       </c>
       <c r="D111" t="s" s="0">
-        <v>199</v>
+        <v>129</v>
       </c>
       <c r="E111" t="s" s="0">
-        <v>59</v>
+        <v>179</v>
       </c>
       <c r="F111" t="n" s="0">
-        <v>1.0</v>
-      </c>
-      <c r="G111" s="9"/>
+        <v>3.0</v>
+      </c>
+      <c r="G111" s="42"/>
     </row>
     <row r="112">
       <c r="A112" t="s" s="0">
-        <v>197</v>
+        <v>175</v>
       </c>
       <c r="B112" t="s" s="0">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="C112" t="s" s="0">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="D112" t="s" s="0">
-        <v>199</v>
+        <v>129</v>
       </c>
       <c r="E112" t="s" s="0">
-        <v>202</v>
+        <v>179</v>
       </c>
       <c r="F112" t="n" s="0">
-        <v>22.0</v>
-      </c>
-      <c r="G112" s="6"/>
+        <v>1.0</v>
+      </c>
+      <c r="G112" s="43"/>
     </row>
     <row r="113">
       <c r="A113" t="s" s="0">
-        <v>197</v>
+        <v>175</v>
       </c>
       <c r="B113" t="s" s="0">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="C113" t="s" s="0">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="D113" t="s" s="0">
-        <v>199</v>
+        <v>129</v>
       </c>
       <c r="E113" t="s" s="0">
-        <v>202</v>
+        <v>179</v>
       </c>
       <c r="F113" t="n" s="0">
-        <v>83.0</v>
-      </c>
-      <c r="G113" s="7"/>
+        <v>2.0</v>
+      </c>
+      <c r="G113" s="44"/>
     </row>
     <row r="114">
       <c r="A114" t="s" s="0">
-        <v>197</v>
+        <v>175</v>
       </c>
       <c r="B114" t="s" s="0">
-        <v>205</v>
+        <v>214</v>
       </c>
       <c r="C114" t="s" s="0">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c r="D114" t="s" s="0">
-        <v>199</v>
+        <v>129</v>
       </c>
       <c r="E114" t="s" s="0">
-        <v>202</v>
+        <v>179</v>
       </c>
       <c r="F114" t="n" s="0">
-        <v>111.0</v>
-      </c>
-      <c r="G114" s="8"/>
+        <v>2.0</v>
+      </c>
+      <c r="G114" s="45"/>
     </row>
     <row r="115">
       <c r="A115" t="s" s="0">
-        <v>197</v>
+        <v>175</v>
       </c>
       <c r="B115" t="s" s="0">
-        <v>207</v>
+        <v>216</v>
       </c>
       <c r="C115" t="s" s="0">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="D115" t="s" s="0">
-        <v>199</v>
+        <v>129</v>
       </c>
       <c r="E115" t="s" s="0">
-        <v>202</v>
+        <v>179</v>
       </c>
       <c r="F115" t="n" s="0">
-        <v>240.0</v>
-      </c>
-      <c r="G115" s="9"/>
+        <v>2.0</v>
+      </c>
+      <c r="G115" s="46"/>
     </row>
     <row r="116">
       <c r="A116" t="s" s="0">
-        <v>197</v>
+        <v>175</v>
       </c>
       <c r="B116" t="s" s="0">
-        <v>209</v>
+        <v>218</v>
       </c>
       <c r="C116" t="s" s="0">
-        <v>157</v>
+        <v>200</v>
       </c>
       <c r="D116" t="s" s="0">
-        <v>199</v>
+        <v>129</v>
       </c>
       <c r="E116" t="s" s="0">
-        <v>202</v>
+        <v>179</v>
       </c>
       <c r="F116" t="n" s="0">
-        <v>119.0</v>
-      </c>
-      <c r="G116" s="45"/>
+        <v>1.0</v>
+      </c>
+      <c r="G116" s="37"/>
     </row>
     <row r="117">
       <c r="A117" t="s" s="0">
-        <v>197</v>
+        <v>175</v>
       </c>
       <c r="B117" t="s" s="0">
-        <v>210</v>
+        <v>219</v>
       </c>
       <c r="C117" t="s" s="0">
-        <v>211</v>
+        <v>200</v>
       </c>
       <c r="D117" t="s" s="0">
-        <v>199</v>
+        <v>129</v>
       </c>
       <c r="E117" t="s" s="0">
-        <v>202</v>
+        <v>179</v>
       </c>
       <c r="F117" t="n" s="0">
-        <v>8.0</v>
-      </c>
-      <c r="G117" s="10"/>
+        <v>3.0</v>
+      </c>
+      <c r="G117" s="37"/>
     </row>
     <row r="118">
       <c r="A118" t="s" s="0">
-        <v>197</v>
+        <v>175</v>
       </c>
       <c r="B118" t="s" s="0">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="C118" t="s" s="0">
-        <v>213</v>
+        <v>200</v>
       </c>
       <c r="D118" t="s" s="0">
-        <v>199</v>
+        <v>129</v>
       </c>
       <c r="E118" t="s" s="0">
-        <v>202</v>
+        <v>179</v>
       </c>
       <c r="F118" t="n" s="0">
-        <v>628.0</v>
-      </c>
-      <c r="G118" s="11"/>
+        <v>2.0</v>
+      </c>
+      <c r="G118" s="37"/>
     </row>
     <row r="119">
       <c r="A119" t="s" s="0">
-        <v>197</v>
+        <v>175</v>
       </c>
       <c r="B119" t="s" s="0">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="C119" t="s" s="0">
-        <v>215</v>
+        <v>52</v>
       </c>
       <c r="D119" t="s" s="0">
-        <v>199</v>
+        <v>129</v>
       </c>
       <c r="E119" t="s" s="0">
-        <v>202</v>
+        <v>179</v>
       </c>
       <c r="F119" t="n" s="0">
-        <v>16.0</v>
-      </c>
-      <c r="G119" s="12"/>
+        <v>7.0</v>
+      </c>
+      <c r="G119" s="9"/>
     </row>
     <row r="120">
       <c r="A120" t="s" s="0">
-        <v>197</v>
+        <v>175</v>
       </c>
       <c r="B120" t="s" s="0">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="C120" t="s" s="0">
-        <v>217</v>
+        <v>181</v>
       </c>
       <c r="D120" t="s" s="0">
-        <v>199</v>
+        <v>129</v>
       </c>
       <c r="E120" t="s" s="0">
-        <v>202</v>
+        <v>179</v>
       </c>
       <c r="F120" t="n" s="0">
-        <v>443.0</v>
-      </c>
-      <c r="G120" s="13"/>
+        <v>9.0</v>
+      </c>
+      <c r="G120" s="25"/>
     </row>
     <row r="121">
       <c r="A121" t="s" s="0">
-        <v>197</v>
+        <v>175</v>
       </c>
       <c r="B121" t="s" s="0">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="C121" t="s" s="0">
-        <v>219</v>
+        <v>52</v>
       </c>
       <c r="D121" t="s" s="0">
-        <v>199</v>
+        <v>129</v>
       </c>
       <c r="E121" t="s" s="0">
-        <v>93</v>
+        <v>179</v>
       </c>
       <c r="F121" t="n" s="0">
         <v>2.0</v>
       </c>
-      <c r="G121" s="14"/>
+      <c r="G121" s="9"/>
     </row>
     <row r="122">
       <c r="A122" t="s" s="0">
-        <v>197</v>
+        <v>175</v>
       </c>
       <c r="B122" t="s" s="0">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="C122" t="s" s="0">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="D122" t="s" s="0">
-        <v>199</v>
+        <v>129</v>
       </c>
       <c r="E122" t="s" s="0">
-        <v>93</v>
+        <v>179</v>
       </c>
       <c r="F122" t="n" s="0">
-        <v>3.0</v>
-      </c>
-      <c r="G122" s="15"/>
+        <v>2.0</v>
+      </c>
+      <c r="G122" s="44"/>
     </row>
     <row r="123">
       <c r="A123" t="s" s="0">
-        <v>197</v>
+        <v>175</v>
       </c>
       <c r="B123" t="s" s="0">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="C123" t="s" s="0">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="D123" t="s" s="0">
-        <v>199</v>
+        <v>129</v>
       </c>
       <c r="E123" t="s" s="0">
-        <v>93</v>
+        <v>179</v>
       </c>
       <c r="F123" t="n" s="0">
-        <v>21.0</v>
-      </c>
-      <c r="G123" s="16"/>
+        <v>2.0</v>
+      </c>
+      <c r="G123" s="45"/>
     </row>
     <row r="124">
       <c r="A124" t="s" s="0">
-        <v>197</v>
+        <v>175</v>
       </c>
       <c r="B124" t="s" s="0">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="C124" t="s" s="0">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="D124" t="s" s="0">
-        <v>199</v>
+        <v>129</v>
       </c>
       <c r="E124" t="s" s="0">
-        <v>93</v>
+        <v>179</v>
       </c>
       <c r="F124" t="n" s="0">
-        <v>4.0</v>
-      </c>
-      <c r="G124" s="17"/>
+        <v>2.0</v>
+      </c>
+      <c r="G124" s="46"/>
     </row>
     <row r="125">
       <c r="A125" t="s" s="0">
-        <v>197</v>
+        <v>175</v>
       </c>
       <c r="B125" t="s" s="0">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C125" t="s" s="0">
-        <v>227</v>
+        <v>52</v>
       </c>
       <c r="D125" t="s" s="0">
-        <v>199</v>
+        <v>129</v>
       </c>
       <c r="E125" t="s" s="0">
-        <v>93</v>
+        <v>179</v>
       </c>
       <c r="F125" t="n" s="0">
         <v>2.0</v>
       </c>
-      <c r="G125" s="18"/>
+      <c r="G125" s="9"/>
     </row>
     <row r="126">
       <c r="A126" t="s" s="0">
-        <v>197</v>
+        <v>175</v>
       </c>
       <c r="B126" t="s" s="0">
         <v>228</v>
       </c>
       <c r="C126" t="s" s="0">
-        <v>229</v>
+        <v>52</v>
       </c>
       <c r="D126" t="s" s="0">
-        <v>199</v>
+        <v>129</v>
       </c>
       <c r="E126" t="s" s="0">
-        <v>93</v>
+        <v>179</v>
       </c>
       <c r="F126" t="n" s="0">
-        <v>87.0</v>
-      </c>
-      <c r="G126" s="19"/>
+        <v>2.0</v>
+      </c>
+      <c r="G126" s="9"/>
     </row>
     <row r="127">
       <c r="A127" t="s" s="0">
-        <v>197</v>
+        <v>175</v>
       </c>
       <c r="B127" t="s" s="0">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C127" t="s" s="0">
-        <v>231</v>
+        <v>52</v>
       </c>
       <c r="D127" t="s" s="0">
-        <v>199</v>
+        <v>129</v>
       </c>
       <c r="E127" t="s" s="0">
-        <v>93</v>
+        <v>179</v>
       </c>
       <c r="F127" t="n" s="0">
-        <v>5.0</v>
-      </c>
-      <c r="G127" s="20"/>
+        <v>2.0</v>
+      </c>
+      <c r="G127" s="9"/>
     </row>
     <row r="128">
       <c r="A128" t="s" s="0">
-        <v>197</v>
+        <v>175</v>
       </c>
       <c r="B128" t="s" s="0">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C128" t="s" s="0">
-        <v>233</v>
+        <v>145</v>
       </c>
       <c r="D128" t="s" s="0">
-        <v>199</v>
+        <v>129</v>
       </c>
       <c r="E128" t="s" s="0">
-        <v>93</v>
+        <v>130</v>
       </c>
       <c r="F128" t="n" s="0">
-        <v>6.0</v>
-      </c>
-      <c r="G128" s="21"/>
+        <v>37.0</v>
+      </c>
+      <c r="G128" s="36"/>
     </row>
     <row r="129">
       <c r="A129" t="s" s="0">
-        <v>197</v>
+        <v>175</v>
       </c>
       <c r="B129" t="s" s="0">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="C129" t="s" s="0">
-        <v>235</v>
+        <v>198</v>
       </c>
       <c r="D129" t="s" s="0">
-        <v>199</v>
+        <v>129</v>
       </c>
       <c r="E129" t="s" s="0">
-        <v>93</v>
+        <v>179</v>
       </c>
       <c r="F129" t="n" s="0">
-        <v>2.0</v>
-      </c>
-      <c r="G129" s="22"/>
+        <v>33.0</v>
+      </c>
+      <c r="G129" s="36"/>
     </row>
     <row r="130">
       <c r="A130" t="s" s="0">
-        <v>197</v>
+        <v>175</v>
       </c>
       <c r="B130" t="s" s="0">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="C130" t="s" s="0">
-        <v>237</v>
+        <v>208</v>
       </c>
       <c r="D130" t="s" s="0">
-        <v>199</v>
+        <v>129</v>
       </c>
       <c r="E130" t="s" s="0">
-        <v>93</v>
+        <v>179</v>
       </c>
       <c r="F130" t="n" s="0">
-        <v>28.0</v>
-      </c>
-      <c r="G130" s="23"/>
+        <v>34.0</v>
+      </c>
+      <c r="G130" s="42"/>
     </row>
     <row r="131">
       <c r="A131" t="s" s="0">
-        <v>197</v>
+        <v>175</v>
       </c>
       <c r="B131" t="s" s="0">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="C131" t="s" s="0">
-        <v>239</v>
+        <v>52</v>
       </c>
       <c r="D131" t="s" s="0">
-        <v>199</v>
+        <v>129</v>
       </c>
       <c r="E131" t="s" s="0">
-        <v>93</v>
+        <v>179</v>
       </c>
       <c r="F131" t="n" s="0">
-        <v>14.0</v>
-      </c>
-      <c r="G131" s="24"/>
+        <v>2.0</v>
+      </c>
+      <c r="G131" s="9"/>
     </row>
     <row r="132">
       <c r="A132" t="s" s="0">
-        <v>197</v>
+        <v>175</v>
       </c>
       <c r="B132" t="s" s="0">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="C132" t="s" s="0">
-        <v>84</v>
+        <v>52</v>
       </c>
       <c r="D132" t="s" s="0">
-        <v>199</v>
+        <v>129</v>
       </c>
       <c r="E132" t="s" s="0">
-        <v>86</v>
+        <v>182</v>
       </c>
       <c r="F132" t="n" s="0">
-        <v>33.0</v>
-      </c>
-      <c r="G132" s="24"/>
+        <v>2.0</v>
+      </c>
+      <c r="G132" s="9"/>
     </row>
     <row r="133">
       <c r="A133" t="s" s="0">
-        <v>241</v>
+        <v>175</v>
       </c>
       <c r="B133" t="s" s="0">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="C133" t="s" s="0">
-        <v>242</v>
+        <v>52</v>
       </c>
       <c r="D133" t="s" s="0">
-        <v>243</v>
+        <v>129</v>
       </c>
       <c r="E133" t="s" s="0">
-        <v>43</v>
+        <v>179</v>
       </c>
       <c r="F133" t="n" s="0">
-        <v>1.0</v>
-      </c>
-      <c r="G133" s="25"/>
+        <v>4.0</v>
+      </c>
+      <c r="G133" s="9"/>
     </row>
     <row r="134">
       <c r="A134" t="s" s="0">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="B134" t="s" s="0">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="C134" t="s" s="0">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="D134" t="s" s="0">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="E134" t="s" s="0">
-        <v>43</v>
+        <v>240</v>
       </c>
       <c r="F134" t="n" s="0">
-        <v>2.0</v>
-      </c>
-      <c r="G134" s="26"/>
+        <v>23.0</v>
+      </c>
+      <c r="G134" s="47"/>
     </row>
     <row r="135">
       <c r="A135" t="s" s="0">
+        <v>236</v>
+      </c>
+      <c r="B135" t="s" s="0">
         <v>241</v>
       </c>
-      <c r="B135" t="s" s="0">
-        <v>245</v>
-      </c>
       <c r="C135" t="s" s="0">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="D135" t="s" s="0">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="E135" t="s" s="0">
-        <v>43</v>
+        <v>240</v>
       </c>
       <c r="F135" t="n" s="0">
-        <v>1.0</v>
-      </c>
-      <c r="G135" s="27"/>
+        <v>281.0</v>
+      </c>
+      <c r="G135" s="48"/>
     </row>
     <row r="136">
       <c r="A136" t="s" s="0">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="B136" t="s" s="0">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C136" t="s" s="0">
-        <v>139</v>
+        <v>244</v>
       </c>
       <c r="D136" t="s" s="0">
-        <v>70</v>
+        <v>239</v>
       </c>
       <c r="E136" t="s" s="0">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="F136" t="n" s="0">
-        <v>19.0</v>
-      </c>
-      <c r="G136" s="42"/>
+        <v>519.0</v>
+      </c>
+      <c r="G136" s="49"/>
     </row>
     <row r="137">
       <c r="A137" t="s" s="0">
+        <v>236</v>
+      </c>
+      <c r="B137" t="s" s="0">
+        <v>245</v>
+      </c>
+      <c r="C137" t="s" s="0">
         <v>246</v>
       </c>
-      <c r="B137" t="s" s="0">
-        <v>249</v>
-      </c>
-      <c r="C137" t="s" s="0">
-        <v>28</v>
-      </c>
       <c r="D137" t="s" s="0">
-        <v>70</v>
+        <v>239</v>
       </c>
       <c r="E137" t="s" s="0">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="F137" t="n" s="0">
-        <v>9.0</v>
-      </c>
-      <c r="G137" s="9"/>
+        <v>23.0</v>
+      </c>
+      <c r="G137" s="50"/>
     </row>
     <row r="138">
       <c r="A138" t="s" s="0">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="B138" t="s" s="0">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="C138" t="s" s="0">
-        <v>28</v>
+        <v>248</v>
       </c>
       <c r="D138" t="s" s="0">
-        <v>70</v>
+        <v>239</v>
       </c>
       <c r="E138" t="s" s="0">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="F138" t="n" s="0">
-        <v>16.0</v>
-      </c>
-      <c r="G138" s="9"/>
+        <v>563.0</v>
+      </c>
+      <c r="G138" s="51"/>
     </row>
     <row r="139">
       <c r="A139" t="s" s="0">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="B139" t="s" s="0">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C139" t="s" s="0">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="D139" t="s" s="0">
-        <v>70</v>
+        <v>239</v>
       </c>
       <c r="E139" t="s" s="0">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="F139" t="n" s="0">
-        <v>1.0</v>
-      </c>
-      <c r="G139" s="28"/>
+        <v>120.0</v>
+      </c>
+      <c r="G139" s="2"/>
     </row>
     <row r="140">
       <c r="A140" t="s" s="0">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="B140" t="s" s="0">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C140" t="s" s="0">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="D140" t="s" s="0">
-        <v>70</v>
+        <v>239</v>
       </c>
       <c r="E140" t="s" s="0">
-        <v>93</v>
+        <v>240</v>
       </c>
       <c r="F140" t="n" s="0">
-        <v>1.0</v>
-      </c>
-      <c r="G140" s="29"/>
+        <v>520.0</v>
+      </c>
+      <c r="G140" s="3"/>
     </row>
     <row r="141">
       <c r="A141" t="s" s="0">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="B141" t="s" s="0">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C141" t="s" s="0">
         <v>254</v>
       </c>
       <c r="D141" t="s" s="0">
-        <v>70</v>
+        <v>239</v>
       </c>
       <c r="E141" t="s" s="0">
-        <v>93</v>
+        <v>240</v>
       </c>
       <c r="F141" t="n" s="0">
-        <v>2.0</v>
-      </c>
-      <c r="G141" s="29"/>
+        <v>97.0</v>
+      </c>
+      <c r="G141" s="5"/>
     </row>
     <row r="142">
       <c r="A142" t="s" s="0">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="B142" t="s" s="0">
         <v>256</v>
@@ -4507,666 +4744,1569 @@
         <v>257</v>
       </c>
       <c r="D142" t="s" s="0">
-        <v>70</v>
+        <v>258</v>
       </c>
       <c r="E142" t="s" s="0">
-        <v>62</v>
+        <v>259</v>
       </c>
       <c r="F142" t="n" s="0">
-        <v>6.0</v>
-      </c>
-      <c r="G142" s="30"/>
+        <v>22.0</v>
+      </c>
+      <c r="G142" s="6"/>
     </row>
     <row r="143">
       <c r="A143" t="s" s="0">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="B143" t="s" s="0">
+        <v>260</v>
+      </c>
+      <c r="C143" t="s" s="0">
+        <v>261</v>
+      </c>
+      <c r="D143" t="s" s="0">
         <v>258</v>
       </c>
-      <c r="C143" t="s" s="0">
+      <c r="E143" t="s" s="0">
         <v>259</v>
       </c>
-      <c r="D143" t="s" s="0">
-        <v>70</v>
-      </c>
-      <c r="E143" t="s" s="0">
-        <v>62</v>
-      </c>
       <c r="F143" t="n" s="0">
-        <v>5.0</v>
-      </c>
-      <c r="G143" s="31"/>
+        <v>125.0</v>
+      </c>
+      <c r="G143" s="7"/>
     </row>
     <row r="144">
       <c r="A144" t="s" s="0">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="B144" t="s" s="0">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="C144" t="s" s="0">
-        <v>28</v>
+        <v>263</v>
       </c>
       <c r="D144" t="s" s="0">
-        <v>70</v>
+        <v>258</v>
       </c>
       <c r="E144" t="s" s="0">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="F144" t="n" s="0">
-        <v>17.0</v>
-      </c>
-      <c r="G144" s="9"/>
+        <v>45.0</v>
+      </c>
+      <c r="G144" s="8"/>
     </row>
     <row r="145">
       <c r="A145" t="s" s="0">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="B145" t="s" s="0">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="C145" t="s" s="0">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="D145" t="s" s="0">
-        <v>70</v>
+        <v>258</v>
       </c>
       <c r="E145" t="s" s="0">
-        <v>26</v>
+        <v>259</v>
       </c>
       <c r="F145" t="n" s="0">
-        <v>5.0</v>
-      </c>
-      <c r="G145" s="32"/>
+        <v>34.0</v>
+      </c>
+      <c r="G145" s="40"/>
     </row>
     <row r="146">
       <c r="A146" t="s" s="0">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="B146" t="s" s="0">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="C146" t="s" s="0">
-        <v>28</v>
+        <v>267</v>
       </c>
       <c r="D146" t="s" s="0">
-        <v>70</v>
+        <v>258</v>
       </c>
       <c r="E146" t="s" s="0">
-        <v>26</v>
+        <v>259</v>
       </c>
       <c r="F146" t="n" s="0">
-        <v>2.0</v>
-      </c>
-      <c r="G146" s="9"/>
+        <v>19.0</v>
+      </c>
+      <c r="G146" s="41"/>
     </row>
     <row r="147">
       <c r="A147" t="s" s="0">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="B147" t="s" s="0">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="C147" t="s" s="0">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="D147" t="s" s="0">
-        <v>70</v>
+        <v>258</v>
       </c>
       <c r="E147" t="s" s="0">
-        <v>26</v>
+        <v>259</v>
       </c>
       <c r="F147" t="n" s="0">
-        <v>10.0</v>
-      </c>
-      <c r="G147" s="33"/>
+        <v>35.0</v>
+      </c>
+      <c r="G147" s="12"/>
     </row>
     <row r="148">
       <c r="A148" t="s" s="0">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="B148" t="s" s="0">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="C148" t="s" s="0">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="D148" t="s" s="0">
-        <v>70</v>
+        <v>258</v>
       </c>
       <c r="E148" t="s" s="0">
-        <v>26</v>
+        <v>259</v>
       </c>
       <c r="F148" t="n" s="0">
-        <v>1.0</v>
-      </c>
-      <c r="G148" s="34"/>
+        <v>447.0</v>
+      </c>
+      <c r="G148" s="13"/>
     </row>
     <row r="149">
       <c r="A149" t="s" s="0">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="B149" t="s" s="0">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="C149" t="s" s="0">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="D149" t="s" s="0">
-        <v>70</v>
+        <v>258</v>
       </c>
       <c r="E149" t="s" s="0">
-        <v>26</v>
+        <v>182</v>
       </c>
       <c r="F149" t="n" s="0">
-        <v>4.0</v>
-      </c>
-      <c r="G149" s="35"/>
+        <v>2.0</v>
+      </c>
+      <c r="G149" s="14"/>
     </row>
     <row r="150">
       <c r="A150" t="s" s="0">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="B150" t="s" s="0">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="C150" t="s" s="0">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="D150" t="s" s="0">
-        <v>70</v>
+        <v>258</v>
       </c>
       <c r="E150" t="s" s="0">
-        <v>26</v>
+        <v>182</v>
       </c>
       <c r="F150" t="n" s="0">
-        <v>27.0</v>
-      </c>
-      <c r="G150" s="36"/>
+        <v>3.0</v>
+      </c>
+      <c r="G150" s="15"/>
     </row>
     <row r="151">
       <c r="A151" t="s" s="0">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="B151" t="s" s="0">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="C151" t="s" s="0">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="D151" t="s" s="0">
-        <v>70</v>
+        <v>258</v>
       </c>
       <c r="E151" t="s" s="0">
-        <v>26</v>
+        <v>182</v>
       </c>
       <c r="F151" t="n" s="0">
-        <v>2.0</v>
-      </c>
-      <c r="G151" s="37"/>
+        <v>21.0</v>
+      </c>
+      <c r="G151" s="16"/>
     </row>
     <row r="152">
       <c r="A152" t="s" s="0">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="B152" t="s" s="0">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="C152" t="s" s="0">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="D152" t="s" s="0">
-        <v>70</v>
+        <v>258</v>
       </c>
       <c r="E152" t="s" s="0">
-        <v>26</v>
+        <v>182</v>
       </c>
       <c r="F152" t="n" s="0">
-        <v>1.0</v>
-      </c>
-      <c r="G152" s="38"/>
+        <v>4.0</v>
+      </c>
+      <c r="G152" s="17"/>
     </row>
     <row r="153">
       <c r="A153" t="s" s="0">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="B153" t="s" s="0">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="C153" t="s" s="0">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="D153" t="s" s="0">
-        <v>70</v>
+        <v>258</v>
       </c>
       <c r="E153" t="s" s="0">
-        <v>26</v>
+        <v>182</v>
       </c>
       <c r="F153" t="n" s="0">
-        <v>5.0</v>
-      </c>
-      <c r="G153" s="39"/>
+        <v>2.0</v>
+      </c>
+      <c r="G153" s="18"/>
     </row>
     <row r="154">
       <c r="A154" t="s" s="0">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="B154" t="s" s="0">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="C154" t="s" s="0">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="D154" t="s" s="0">
-        <v>70</v>
+        <v>258</v>
       </c>
       <c r="E154" t="s" s="0">
-        <v>26</v>
+        <v>182</v>
       </c>
       <c r="F154" t="n" s="0">
-        <v>4.0</v>
-      </c>
-      <c r="G154" s="40"/>
+        <v>87.0</v>
+      </c>
+      <c r="G154" s="19"/>
     </row>
     <row r="155">
       <c r="A155" t="s" s="0">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="B155" t="s" s="0">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="C155" t="s" s="0">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="D155" t="s" s="0">
-        <v>70</v>
+        <v>258</v>
       </c>
       <c r="E155" t="s" s="0">
-        <v>26</v>
+        <v>182</v>
       </c>
       <c r="F155" t="n" s="0">
-        <v>1.0</v>
-      </c>
-      <c r="G155" s="41"/>
+        <v>5.0</v>
+      </c>
+      <c r="G155" s="20"/>
     </row>
     <row r="156">
       <c r="A156" t="s" s="0">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="B156" t="s" s="0">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="C156" t="s" s="0">
-        <v>28</v>
+        <v>287</v>
       </c>
       <c r="D156" t="s" s="0">
-        <v>70</v>
+        <v>258</v>
       </c>
       <c r="E156" t="s" s="0">
-        <v>26</v>
+        <v>182</v>
       </c>
       <c r="F156" t="n" s="0">
-        <v>3.0</v>
-      </c>
-      <c r="G156" s="9"/>
+        <v>6.0</v>
+      </c>
+      <c r="G156" s="21"/>
     </row>
     <row r="157">
       <c r="A157" t="s" s="0">
-        <v>284</v>
+        <v>255</v>
       </c>
       <c r="B157" t="s" s="0">
-        <v>212</v>
+        <v>288</v>
       </c>
       <c r="C157" t="s" s="0">
-        <v>213</v>
+        <v>289</v>
       </c>
       <c r="D157" t="s" s="0">
-        <v>199</v>
+        <v>258</v>
       </c>
       <c r="E157" t="s" s="0">
-        <v>202</v>
+        <v>182</v>
       </c>
       <c r="F157" t="n" s="0">
-        <v>11.0</v>
-      </c>
-      <c r="G157" s="11"/>
+        <v>2.0</v>
+      </c>
+      <c r="G157" s="22"/>
     </row>
     <row r="158">
       <c r="A158" t="s" s="0">
-        <v>285</v>
+        <v>255</v>
       </c>
       <c r="B158" t="s" s="0">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="C158" t="s" s="0">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="D158" t="s" s="0">
-        <v>287</v>
+        <v>258</v>
       </c>
       <c r="E158" t="s" s="0">
-        <v>288</v>
+        <v>182</v>
       </c>
       <c r="F158" t="n" s="0">
-        <v>17.0</v>
-      </c>
-      <c r="G158" s="42"/>
+        <v>30.0</v>
+      </c>
+      <c r="G158" s="23"/>
     </row>
     <row r="159">
       <c r="A159" t="s" s="0">
-        <v>285</v>
+        <v>255</v>
       </c>
       <c r="B159" t="s" s="0">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="C159" t="s" s="0">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="D159" t="s" s="0">
-        <v>287</v>
+        <v>258</v>
       </c>
       <c r="E159" t="s" s="0">
-        <v>29</v>
+        <v>182</v>
       </c>
       <c r="F159" t="n" s="0">
-        <v>1.0</v>
-      </c>
-      <c r="G159" s="43"/>
+        <v>14.0</v>
+      </c>
+      <c r="G159" s="24"/>
     </row>
     <row r="160">
       <c r="A160" t="s" s="0">
-        <v>285</v>
+        <v>294</v>
       </c>
       <c r="B160" t="s" s="0">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="C160" t="s" s="0">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="D160" t="s" s="0">
-        <v>287</v>
+        <v>28</v>
       </c>
       <c r="E160" t="s" s="0">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="F160" t="n" s="0">
         <v>1.0</v>
       </c>
-      <c r="G160" s="44"/>
+      <c r="G160" s="42"/>
     </row>
     <row r="161">
       <c r="A161" t="s" s="0">
-        <v>285</v>
+        <v>294</v>
       </c>
       <c r="B161" t="s" s="0">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="C161" t="s" s="0">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="D161" t="s" s="0">
-        <v>287</v>
+        <v>28</v>
       </c>
       <c r="E161" t="s" s="0">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="F161" t="n" s="0">
-        <v>9.0</v>
-      </c>
-      <c r="G161" s="45"/>
+        <v>2.0</v>
+      </c>
+      <c r="G161" s="43"/>
     </row>
     <row r="162">
       <c r="A162" t="s" s="0">
-        <v>285</v>
+        <v>294</v>
       </c>
       <c r="B162" t="s" s="0">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="C162" t="s" s="0">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="D162" t="s" s="0">
-        <v>287</v>
+        <v>28</v>
       </c>
       <c r="E162" t="s" s="0">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F162" t="n" s="0">
-        <v>6.0</v>
-      </c>
-      <c r="G162" s="46"/>
+        <v>1.0</v>
+      </c>
+      <c r="G162" s="44"/>
     </row>
     <row r="163">
       <c r="A163" t="s" s="0">
-        <v>285</v>
+        <v>298</v>
       </c>
       <c r="B163" t="s" s="0">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="C163" t="s" s="0">
-        <v>293</v>
+        <v>300</v>
       </c>
       <c r="D163" t="s" s="0">
-        <v>287</v>
+        <v>301</v>
       </c>
       <c r="E163" t="s" s="0">
-        <v>288</v>
+        <v>302</v>
       </c>
       <c r="F163" t="n" s="0">
-        <v>4.0</v>
-      </c>
-      <c r="G163" s="47"/>
+        <v>19.0</v>
+      </c>
+      <c r="G163" s="45"/>
     </row>
     <row r="164">
       <c r="A164" t="s" s="0">
-        <v>285</v>
+        <v>298</v>
       </c>
       <c r="B164" t="s" s="0">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="C164" t="s" s="0">
-        <v>294</v>
+        <v>304</v>
       </c>
       <c r="D164" t="s" s="0">
-        <v>287</v>
+        <v>301</v>
       </c>
       <c r="E164" t="s" s="0">
-        <v>288</v>
+        <v>302</v>
       </c>
       <c r="F164" t="n" s="0">
-        <v>2.0</v>
-      </c>
-      <c r="G164" s="48"/>
+        <v>9.0</v>
+      </c>
+      <c r="G164" s="46"/>
     </row>
     <row r="165">
       <c r="A165" t="s" s="0">
-        <v>285</v>
+        <v>298</v>
       </c>
       <c r="B165" t="s" s="0">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="C165" t="s" s="0">
-        <v>295</v>
+        <v>306</v>
       </c>
       <c r="D165" t="s" s="0">
-        <v>287</v>
+        <v>301</v>
       </c>
       <c r="E165" t="s" s="0">
-        <v>288</v>
+        <v>302</v>
       </c>
       <c r="F165" t="n" s="0">
-        <v>31.0</v>
-      </c>
-      <c r="G165" s="49"/>
+        <v>16.0</v>
+      </c>
+      <c r="G165" s="35"/>
     </row>
     <row r="166">
       <c r="A166" t="s" s="0">
-        <v>285</v>
+        <v>298</v>
       </c>
       <c r="B166" t="s" s="0">
-        <v>296</v>
+        <v>307</v>
       </c>
       <c r="C166" t="s" s="0">
-        <v>296</v>
+        <v>308</v>
       </c>
       <c r="D166" t="s" s="0">
-        <v>287</v>
+        <v>301</v>
       </c>
       <c r="E166" t="s" s="0">
-        <v>288</v>
+        <v>302</v>
       </c>
       <c r="F166" t="n" s="0">
-        <v>4.0</v>
-      </c>
-      <c r="G166" s="50"/>
+        <v>1.0</v>
+      </c>
+      <c r="G166" s="38"/>
     </row>
     <row r="167">
       <c r="A167" t="s" s="0">
-        <v>285</v>
+        <v>298</v>
       </c>
       <c r="B167" t="s" s="0">
-        <v>297</v>
+        <v>309</v>
       </c>
       <c r="C167" t="s" s="0">
-        <v>297</v>
+        <v>310</v>
       </c>
       <c r="D167" t="s" s="0">
-        <v>287</v>
+        <v>301</v>
       </c>
       <c r="E167" t="s" s="0">
-        <v>59</v>
+        <v>182</v>
       </c>
       <c r="F167" t="n" s="0">
-        <v>1.0</v>
-      </c>
-      <c r="G167" s="51"/>
+        <v>2.0</v>
+      </c>
+      <c r="G167" s="47"/>
     </row>
     <row r="168">
       <c r="A168" t="s" s="0">
-        <v>285</v>
+        <v>298</v>
       </c>
       <c r="B168" t="s" s="0">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="C168" t="s" s="0">
-        <v>298</v>
+        <v>312</v>
       </c>
       <c r="D168" t="s" s="0">
-        <v>287</v>
+        <v>301</v>
       </c>
       <c r="E168" t="s" s="0">
-        <v>59</v>
+        <v>182</v>
       </c>
       <c r="F168" t="n" s="0">
         <v>1.0</v>
       </c>
-      <c r="G168" s="2"/>
+      <c r="G168" s="48"/>
     </row>
     <row r="169">
       <c r="A169" t="s" s="0">
-        <v>285</v>
+        <v>298</v>
       </c>
       <c r="B169" t="s" s="0">
-        <v>299</v>
+        <v>313</v>
       </c>
       <c r="C169" t="s" s="0">
-        <v>299</v>
+        <v>314</v>
       </c>
       <c r="D169" t="s" s="0">
-        <v>287</v>
+        <v>301</v>
       </c>
       <c r="E169" t="s" s="0">
-        <v>288</v>
+        <v>86</v>
       </c>
       <c r="F169" t="n" s="0">
-        <v>12.0</v>
-      </c>
-      <c r="G169" s="3"/>
+        <v>6.0</v>
+      </c>
+      <c r="G169" s="49"/>
     </row>
     <row r="170">
       <c r="A170" t="s" s="0">
-        <v>285</v>
+        <v>298</v>
       </c>
       <c r="B170" t="s" s="0">
-        <v>300</v>
+        <v>315</v>
       </c>
       <c r="C170" t="s" s="0">
-        <v>300</v>
+        <v>316</v>
       </c>
       <c r="D170" t="s" s="0">
-        <v>287</v>
+        <v>301</v>
       </c>
       <c r="E170" t="s" s="0">
-        <v>301</v>
+        <v>86</v>
       </c>
       <c r="F170" t="n" s="0">
-        <v>1.0</v>
-      </c>
-      <c r="G170" s="4"/>
+        <v>5.0</v>
+      </c>
+      <c r="G170" s="50"/>
     </row>
     <row r="171">
       <c r="A171" t="s" s="0">
-        <v>285</v>
+        <v>298</v>
       </c>
       <c r="B171" t="s" s="0">
-        <v>302</v>
+        <v>317</v>
       </c>
       <c r="C171" t="s" s="0">
-        <v>302</v>
+        <v>318</v>
       </c>
       <c r="D171" t="s" s="0">
-        <v>287</v>
+        <v>301</v>
       </c>
       <c r="E171" t="s" s="0">
-        <v>303</v>
+        <v>319</v>
       </c>
       <c r="F171" t="n" s="0">
-        <v>1.0</v>
-      </c>
-      <c r="G171" s="5"/>
+        <v>17.0</v>
+      </c>
+      <c r="G171" s="51"/>
     </row>
     <row r="172">
       <c r="A172" t="s" s="0">
-        <v>285</v>
+        <v>320</v>
       </c>
       <c r="B172" t="s" s="0">
-        <v>304</v>
+        <v>321</v>
       </c>
       <c r="C172" t="s" s="0">
-        <v>304</v>
+        <v>52</v>
       </c>
       <c r="D172" t="s" s="0">
-        <v>287</v>
+        <v>301</v>
       </c>
       <c r="E172" t="s" s="0">
-        <v>303</v>
+        <v>111</v>
       </c>
       <c r="F172" t="n" s="0">
-        <v>1.0</v>
-      </c>
-      <c r="G172" s="6"/>
+        <v>2.0</v>
+      </c>
+      <c r="G172" s="9"/>
     </row>
     <row r="173">
       <c r="A173" t="s" s="0">
-        <v>285</v>
+        <v>322</v>
       </c>
       <c r="B173" t="s" s="0">
-        <v>305</v>
+        <v>323</v>
       </c>
       <c r="C173" t="s" s="0">
-        <v>305</v>
+        <v>324</v>
       </c>
       <c r="D173" t="s" s="0">
-        <v>287</v>
+        <v>301</v>
       </c>
       <c r="E173" t="s" s="0">
-        <v>59</v>
+        <v>111</v>
       </c>
       <c r="F173" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="G173" s="32"/>
+    </row>
+    <row r="174">
+      <c r="A174" t="s" s="0">
+        <v>322</v>
+      </c>
+      <c r="B174" t="s" s="0">
+        <v>325</v>
+      </c>
+      <c r="C174" t="s" s="0">
+        <v>326</v>
+      </c>
+      <c r="D174" t="s" s="0">
+        <v>301</v>
+      </c>
+      <c r="E174" t="s" s="0">
+        <v>111</v>
+      </c>
+      <c r="F174" t="n" s="0">
+        <v>11.0</v>
+      </c>
+      <c r="G174" s="33"/>
+    </row>
+    <row r="175">
+      <c r="A175" t="s" s="0">
+        <v>322</v>
+      </c>
+      <c r="B175" t="s" s="0">
+        <v>327</v>
+      </c>
+      <c r="C175" t="s" s="0">
+        <v>328</v>
+      </c>
+      <c r="D175" t="s" s="0">
+        <v>301</v>
+      </c>
+      <c r="E175" t="s" s="0">
+        <v>111</v>
+      </c>
+      <c r="F175" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="G175" s="36"/>
+    </row>
+    <row r="176">
+      <c r="A176" t="s" s="0">
+        <v>322</v>
+      </c>
+      <c r="B176" t="s" s="0">
+        <v>329</v>
+      </c>
+      <c r="C176" t="s" s="0">
+        <v>330</v>
+      </c>
+      <c r="D176" t="s" s="0">
+        <v>301</v>
+      </c>
+      <c r="E176" t="s" s="0">
+        <v>111</v>
+      </c>
+      <c r="F176" t="n" s="0">
+        <v>27.0</v>
+      </c>
+      <c r="G176" s="37"/>
+    </row>
+    <row r="177">
+      <c r="A177" t="s" s="0">
+        <v>322</v>
+      </c>
+      <c r="B177" t="s" s="0">
+        <v>331</v>
+      </c>
+      <c r="C177" t="s" s="0">
+        <v>332</v>
+      </c>
+      <c r="D177" t="s" s="0">
+        <v>301</v>
+      </c>
+      <c r="E177" t="s" s="0">
+        <v>111</v>
+      </c>
+      <c r="F177" t="n" s="0">
         <v>2.0</v>
       </c>
-      <c r="G173" s="7"/>
+      <c r="G177" s="39"/>
+    </row>
+    <row r="178">
+      <c r="A178" t="s" s="0">
+        <v>322</v>
+      </c>
+      <c r="B178" t="s" s="0">
+        <v>333</v>
+      </c>
+      <c r="C178" t="s" s="0">
+        <v>334</v>
+      </c>
+      <c r="D178" t="s" s="0">
+        <v>301</v>
+      </c>
+      <c r="E178" t="s" s="0">
+        <v>111</v>
+      </c>
+      <c r="F178" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G178" s="40"/>
+    </row>
+    <row r="179">
+      <c r="A179" t="s" s="0">
+        <v>322</v>
+      </c>
+      <c r="B179" t="s" s="0">
+        <v>335</v>
+      </c>
+      <c r="C179" t="s" s="0">
+        <v>336</v>
+      </c>
+      <c r="D179" t="s" s="0">
+        <v>301</v>
+      </c>
+      <c r="E179" t="s" s="0">
+        <v>111</v>
+      </c>
+      <c r="F179" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="G179" s="41"/>
+    </row>
+    <row r="180">
+      <c r="A180" t="s" s="0">
+        <v>322</v>
+      </c>
+      <c r="B180" t="s" s="0">
+        <v>337</v>
+      </c>
+      <c r="C180" t="s" s="0">
+        <v>338</v>
+      </c>
+      <c r="D180" t="s" s="0">
+        <v>301</v>
+      </c>
+      <c r="E180" t="s" s="0">
+        <v>111</v>
+      </c>
+      <c r="F180" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="G180" s="42"/>
+    </row>
+    <row r="181">
+      <c r="A181" t="s" s="0">
+        <v>322</v>
+      </c>
+      <c r="B181" t="s" s="0">
+        <v>339</v>
+      </c>
+      <c r="C181" t="s" s="0">
+        <v>340</v>
+      </c>
+      <c r="D181" t="s" s="0">
+        <v>301</v>
+      </c>
+      <c r="E181" t="s" s="0">
+        <v>111</v>
+      </c>
+      <c r="F181" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G181" s="43"/>
+    </row>
+    <row r="182">
+      <c r="A182" t="s" s="0">
+        <v>341</v>
+      </c>
+      <c r="B182" t="s" s="0">
+        <v>256</v>
+      </c>
+      <c r="C182" t="s" s="0">
+        <v>257</v>
+      </c>
+      <c r="D182" t="s" s="0">
+        <v>258</v>
+      </c>
+      <c r="E182" t="s" s="0">
+        <v>259</v>
+      </c>
+      <c r="F182" t="n" s="0">
+        <v>55.0</v>
+      </c>
+      <c r="G182" s="6"/>
+    </row>
+    <row r="183">
+      <c r="A183" t="s" s="0">
+        <v>341</v>
+      </c>
+      <c r="B183" t="s" s="0">
+        <v>260</v>
+      </c>
+      <c r="C183" t="s" s="0">
+        <v>261</v>
+      </c>
+      <c r="D183" t="s" s="0">
+        <v>258</v>
+      </c>
+      <c r="E183" t="s" s="0">
+        <v>259</v>
+      </c>
+      <c r="F183" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="G183" s="7"/>
+    </row>
+    <row r="184">
+      <c r="A184" t="s" s="0">
+        <v>341</v>
+      </c>
+      <c r="B184" t="s" s="0">
+        <v>262</v>
+      </c>
+      <c r="C184" t="s" s="0">
+        <v>263</v>
+      </c>
+      <c r="D184" t="s" s="0">
+        <v>258</v>
+      </c>
+      <c r="E184" t="s" s="0">
+        <v>259</v>
+      </c>
+      <c r="F184" t="n" s="0">
+        <v>41.0</v>
+      </c>
+      <c r="G184" s="8"/>
+    </row>
+    <row r="185">
+      <c r="A185" t="s" s="0">
+        <v>341</v>
+      </c>
+      <c r="B185" t="s" s="0">
+        <v>342</v>
+      </c>
+      <c r="C185" t="s" s="0">
+        <v>343</v>
+      </c>
+      <c r="D185" t="s" s="0">
+        <v>258</v>
+      </c>
+      <c r="E185" t="s" s="0">
+        <v>259</v>
+      </c>
+      <c r="F185" t="n" s="0">
+        <v>14.0</v>
+      </c>
+      <c r="G185" s="2"/>
+    </row>
+    <row r="186">
+      <c r="A186" t="s" s="0">
+        <v>341</v>
+      </c>
+      <c r="B186" t="s" s="0">
+        <v>344</v>
+      </c>
+      <c r="C186" t="s" s="0">
+        <v>345</v>
+      </c>
+      <c r="D186" t="s" s="0">
+        <v>258</v>
+      </c>
+      <c r="E186" t="s" s="0">
+        <v>259</v>
+      </c>
+      <c r="F186" t="n" s="0">
+        <v>91.0</v>
+      </c>
+      <c r="G186" s="9"/>
+    </row>
+    <row r="187">
+      <c r="A187" t="s" s="0">
+        <v>341</v>
+      </c>
+      <c r="B187" t="s" s="0">
+        <v>346</v>
+      </c>
+      <c r="C187" t="s" s="0">
+        <v>347</v>
+      </c>
+      <c r="D187" t="s" s="0">
+        <v>258</v>
+      </c>
+      <c r="E187" t="s" s="0">
+        <v>259</v>
+      </c>
+      <c r="F187" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="G187" s="3"/>
+    </row>
+    <row r="188">
+      <c r="A188" t="s" s="0">
+        <v>341</v>
+      </c>
+      <c r="B188" t="s" s="0">
+        <v>348</v>
+      </c>
+      <c r="C188" t="s" s="0">
+        <v>142</v>
+      </c>
+      <c r="D188" t="s" s="0">
+        <v>258</v>
+      </c>
+      <c r="E188" t="s" s="0">
+        <v>259</v>
+      </c>
+      <c r="F188" t="n" s="0">
+        <v>120.0</v>
+      </c>
+      <c r="G188" s="35"/>
+    </row>
+    <row r="189">
+      <c r="A189" t="s" s="0">
+        <v>341</v>
+      </c>
+      <c r="B189" t="s" s="0">
+        <v>349</v>
+      </c>
+      <c r="C189" t="s" s="0">
+        <v>350</v>
+      </c>
+      <c r="D189" t="s" s="0">
+        <v>258</v>
+      </c>
+      <c r="E189" t="s" s="0">
+        <v>259</v>
+      </c>
+      <c r="F189" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="G189" s="4"/>
+    </row>
+    <row r="190">
+      <c r="A190" t="s" s="0">
+        <v>341</v>
+      </c>
+      <c r="B190" t="s" s="0">
+        <v>351</v>
+      </c>
+      <c r="C190" t="s" s="0">
+        <v>352</v>
+      </c>
+      <c r="D190" t="s" s="0">
+        <v>258</v>
+      </c>
+      <c r="E190" t="s" s="0">
+        <v>259</v>
+      </c>
+      <c r="F190" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="G190" s="10"/>
+    </row>
+    <row r="191">
+      <c r="A191" t="s" s="0">
+        <v>341</v>
+      </c>
+      <c r="B191" t="s" s="0">
+        <v>353</v>
+      </c>
+      <c r="C191" t="s" s="0">
+        <v>354</v>
+      </c>
+      <c r="D191" t="s" s="0">
+        <v>258</v>
+      </c>
+      <c r="E191" t="s" s="0">
+        <v>259</v>
+      </c>
+      <c r="F191" t="n" s="0">
+        <v>711.0</v>
+      </c>
+      <c r="G191" s="11"/>
+    </row>
+    <row r="192">
+      <c r="A192" t="s" s="0">
+        <v>355</v>
+      </c>
+      <c r="B192" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="C192" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="D192" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="E192" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="F192" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="G192" s="12"/>
+    </row>
+    <row r="193">
+      <c r="A193" t="s" s="0">
+        <v>355</v>
+      </c>
+      <c r="B193" t="s" s="0">
+        <v>47</v>
+      </c>
+      <c r="C193" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="D193" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="E193" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="F193" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G193" s="10"/>
+    </row>
+    <row r="194">
+      <c r="A194" t="s" s="0">
+        <v>355</v>
+      </c>
+      <c r="B194" t="s" s="0">
+        <v>356</v>
+      </c>
+      <c r="C194" t="s" s="0">
+        <v>357</v>
+      </c>
+      <c r="D194" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="E194" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="F194" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G194" s="5"/>
+    </row>
+    <row r="195">
+      <c r="A195" t="s" s="0">
+        <v>355</v>
+      </c>
+      <c r="B195" t="s" s="0">
+        <v>358</v>
+      </c>
+      <c r="C195" t="s" s="0">
+        <v>359</v>
+      </c>
+      <c r="D195" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="E195" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="F195" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="G195" s="6"/>
+    </row>
+    <row r="196">
+      <c r="A196" t="s" s="0">
+        <v>355</v>
+      </c>
+      <c r="B196" t="s" s="0">
+        <v>360</v>
+      </c>
+      <c r="C196" t="s" s="0">
+        <v>359</v>
+      </c>
+      <c r="D196" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="E196" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="F196" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G196" s="6"/>
+    </row>
+    <row r="197">
+      <c r="A197" t="s" s="0">
+        <v>355</v>
+      </c>
+      <c r="B197" t="s" s="0">
+        <v>361</v>
+      </c>
+      <c r="C197" t="s" s="0">
+        <v>362</v>
+      </c>
+      <c r="D197" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="E197" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="F197" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G197" s="7"/>
+    </row>
+    <row r="198">
+      <c r="A198" t="s" s="0">
+        <v>355</v>
+      </c>
+      <c r="B198" t="s" s="0">
+        <v>363</v>
+      </c>
+      <c r="C198" t="s" s="0">
+        <v>364</v>
+      </c>
+      <c r="D198" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="E198" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="F198" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G198" s="8"/>
+    </row>
+    <row r="199">
+      <c r="A199" t="s" s="0">
+        <v>355</v>
+      </c>
+      <c r="B199" t="s" s="0">
+        <v>365</v>
+      </c>
+      <c r="C199" t="s" s="0">
+        <v>359</v>
+      </c>
+      <c r="D199" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="E199" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="F199" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G199" s="6"/>
+    </row>
+    <row r="200">
+      <c r="A200" t="s" s="0">
+        <v>355</v>
+      </c>
+      <c r="B200" t="s" s="0">
+        <v>366</v>
+      </c>
+      <c r="C200" t="s" s="0">
+        <v>95</v>
+      </c>
+      <c r="D200" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="E200" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="F200" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G200" s="27"/>
+    </row>
+    <row r="201">
+      <c r="A201" t="s" s="0">
+        <v>355</v>
+      </c>
+      <c r="B201" t="s" s="0">
+        <v>367</v>
+      </c>
+      <c r="C201" t="s" s="0">
+        <v>359</v>
+      </c>
+      <c r="D201" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="E201" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="F201" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G201" s="6"/>
+    </row>
+    <row r="202">
+      <c r="A202" t="s" s="0">
+        <v>355</v>
+      </c>
+      <c r="B202" t="s" s="0">
+        <v>368</v>
+      </c>
+      <c r="C202" t="s" s="0">
+        <v>79</v>
+      </c>
+      <c r="D202" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="E202" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="F202" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G202" s="24"/>
+    </row>
+    <row r="203">
+      <c r="A203" t="s" s="0">
+        <v>355</v>
+      </c>
+      <c r="B203" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="C203" t="s" s="0">
+        <v>79</v>
+      </c>
+      <c r="D203" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="E203" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="F203" t="n" s="0">
+        <v>31.0</v>
+      </c>
+      <c r="G203" s="24"/>
+    </row>
+    <row r="204">
+      <c r="A204" t="s" s="0">
+        <v>355</v>
+      </c>
+      <c r="B204" t="s" s="0">
+        <v>369</v>
+      </c>
+      <c r="C204" t="s" s="0">
+        <v>95</v>
+      </c>
+      <c r="D204" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="E204" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="F204" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G204" s="27"/>
+    </row>
+    <row r="205">
+      <c r="A205" t="s" s="0">
+        <v>355</v>
+      </c>
+      <c r="B205" t="s" s="0">
+        <v>370</v>
+      </c>
+      <c r="C205" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="D205" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="E205" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="F205" t="n" s="0">
+        <v>21.0</v>
+      </c>
+      <c r="G205" s="9"/>
+    </row>
+    <row r="206">
+      <c r="A206" t="s" s="0">
+        <v>355</v>
+      </c>
+      <c r="B206" t="s" s="0">
+        <v>371</v>
+      </c>
+      <c r="C206" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="D206" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="E206" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="F206" t="n" s="0">
+        <v>33.0</v>
+      </c>
+      <c r="G206" s="9"/>
+    </row>
+    <row r="207">
+      <c r="A207" t="s" s="0">
+        <v>355</v>
+      </c>
+      <c r="B207" t="s" s="0">
+        <v>372</v>
+      </c>
+      <c r="C207" t="s" s="0">
+        <v>95</v>
+      </c>
+      <c r="D207" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="E207" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="F207" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G207" s="27"/>
+    </row>
+    <row r="208">
+      <c r="A208" t="s" s="0">
+        <v>355</v>
+      </c>
+      <c r="B208" t="s" s="0">
+        <v>373</v>
+      </c>
+      <c r="C208" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="D208" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="E208" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="F208" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="G208" s="9"/>
+    </row>
+    <row r="209">
+      <c r="A209" t="s" s="0">
+        <v>374</v>
+      </c>
+      <c r="B209" t="s" s="0">
+        <v>67</v>
+      </c>
+      <c r="C209" t="s" s="0">
+        <v>68</v>
+      </c>
+      <c r="D209" t="s" s="0">
+        <v>375</v>
+      </c>
+      <c r="E209" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="F209" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="G209" s="20"/>
+    </row>
+    <row r="210">
+      <c r="A210" t="s" s="0">
+        <v>374</v>
+      </c>
+      <c r="B210" t="s" s="0">
+        <v>376</v>
+      </c>
+      <c r="C210" t="s" s="0">
+        <v>79</v>
+      </c>
+      <c r="D210" t="s" s="0">
+        <v>375</v>
+      </c>
+      <c r="E210" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="F210" t="n" s="0">
+        <v>10.0</v>
+      </c>
+      <c r="G210" s="24"/>
+    </row>
+    <row r="211">
+      <c r="A211" t="s" s="0">
+        <v>377</v>
+      </c>
+      <c r="B211" t="s" s="0">
+        <v>378</v>
+      </c>
+      <c r="C211" t="s" s="0">
+        <v>378</v>
+      </c>
+      <c r="D211" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="E211" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="F211" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="G211" s="9"/>
+    </row>
+    <row r="212">
+      <c r="A212" t="s" s="0">
+        <v>377</v>
+      </c>
+      <c r="B212" t="s" s="0">
+        <v>380</v>
+      </c>
+      <c r="C212" t="s" s="0">
+        <v>380</v>
+      </c>
+      <c r="D212" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="E212" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="F212" t="n" s="0">
+        <v>23.0</v>
+      </c>
+      <c r="G212" s="49"/>
+    </row>
+    <row r="213">
+      <c r="A213" t="s" s="0">
+        <v>377</v>
+      </c>
+      <c r="B213" t="s" s="0">
+        <v>381</v>
+      </c>
+      <c r="C213" t="s" s="0">
+        <v>381</v>
+      </c>
+      <c r="D213" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="E213" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="F213" t="n" s="0">
+        <v>12.0</v>
+      </c>
+      <c r="G213" s="3"/>
+    </row>
+    <row r="214">
+      <c r="A214" t="s" s="0">
+        <v>377</v>
+      </c>
+      <c r="B214" t="s" s="0">
+        <v>382</v>
+      </c>
+      <c r="C214" t="s" s="0">
+        <v>382</v>
+      </c>
+      <c r="D214" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="E214" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="F214" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="G214" s="7"/>
+    </row>
+    <row r="215">
+      <c r="A215" t="s" s="0">
+        <v>377</v>
+      </c>
+      <c r="B215" t="s" s="0">
+        <v>383</v>
+      </c>
+      <c r="C215" t="s" s="0">
+        <v>383</v>
+      </c>
+      <c r="D215" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="E215" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="F215" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G215" s="10"/>
+    </row>
+    <row r="216">
+      <c r="A216" t="s" s="0">
+        <v>377</v>
+      </c>
+      <c r="B216" t="s" s="0">
+        <v>384</v>
+      </c>
+      <c r="C216" t="s" s="0">
+        <v>384</v>
+      </c>
+      <c r="D216" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="E216" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="F216" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="G216" s="11"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
